--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL104"/>
+  <dimension ref="A1:AL105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12252,7 +12252,7 @@
         <v>348.26</v>
       </c>
       <c r="R103" t="n">
-        <v>351.21</v>
+        <v>340.78</v>
       </c>
       <c r="S103" t="n">
         <v>336</v>
@@ -12372,7 +12372,7 @@
         <v>340.66</v>
       </c>
       <c r="R104" t="n">
-        <v>360.83</v>
+        <v>340.38</v>
       </c>
       <c r="S104" t="n">
         <v>339.39</v>
@@ -12399,7 +12399,7 @@
         <v>316.43</v>
       </c>
       <c r="AA104" t="n">
-        <v>291.32</v>
+        <v>301.62</v>
       </c>
       <c r="AB104" t="n">
         <v>298.28</v>
@@ -12426,12 +12426,132 @@
         <v>325.03</v>
       </c>
       <c r="AJ104" t="n">
-        <v>334.59</v>
+        <v>343.47</v>
       </c>
       <c r="AK104" t="n">
         <v>333.45</v>
       </c>
       <c r="AL104" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>295.65</v>
+      </c>
+      <c r="C105" t="n">
+        <v>285.43</v>
+      </c>
+      <c r="D105" t="n">
+        <v>293.84</v>
+      </c>
+      <c r="E105" t="n">
+        <v>315.22</v>
+      </c>
+      <c r="F105" t="n">
+        <v>332.32</v>
+      </c>
+      <c r="G105" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="H105" t="n">
+        <v>350.66</v>
+      </c>
+      <c r="I105" t="n">
+        <v>349.56</v>
+      </c>
+      <c r="J105" t="n">
+        <v>351.8</v>
+      </c>
+      <c r="K105" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="L105" t="n">
+        <v>355.48</v>
+      </c>
+      <c r="M105" t="n">
+        <v>352.15</v>
+      </c>
+      <c r="N105" t="n">
+        <v>348.38</v>
+      </c>
+      <c r="O105" t="n">
+        <v>343.44</v>
+      </c>
+      <c r="P105" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>335.87</v>
+      </c>
+      <c r="R105" t="n">
+        <v>330.21</v>
+      </c>
+      <c r="S105" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="T105" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="U105" t="n">
+        <v>322.77</v>
+      </c>
+      <c r="V105" t="n">
+        <v>322.73</v>
+      </c>
+      <c r="W105" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="X105" t="n">
+        <v>313.74</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>304.29</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>316.94</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>300.7</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>293.24</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>286.05</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>283.04</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>294.41</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>311.14</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>325.83</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>341.78</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>334.68</v>
+      </c>
+      <c r="AL105" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12448,7 +12568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13511,6 +13631,16 @@
       </c>
       <c r="B106" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -13679,28 +13809,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01844238235029206</v>
+        <v>-0.04203941097004492</v>
       </c>
       <c r="J2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L2" t="n">
-        <v>8.990975335354534e-05</v>
+        <v>0.0004724080594854518</v>
       </c>
       <c r="M2" t="n">
-        <v>13.59850516191627</v>
+        <v>13.5828062174127</v>
       </c>
       <c r="N2" t="n">
-        <v>253.8489306416653</v>
+        <v>252.7672320770698</v>
       </c>
       <c r="O2" t="n">
-        <v>15.93263727829343</v>
+        <v>15.89865503987899</v>
       </c>
       <c r="P2" t="n">
-        <v>309.0910786901956</v>
+        <v>309.2991375900362</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13757,28 +13887,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07014768304424659</v>
+        <v>0.03943518791290231</v>
       </c>
       <c r="J3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001105580779811155</v>
+        <v>0.0003519537109034632</v>
       </c>
       <c r="M3" t="n">
-        <v>13.58202064011468</v>
+        <v>13.60583811903392</v>
       </c>
       <c r="N3" t="n">
-        <v>292.6334150118266</v>
+        <v>292.5923064269153</v>
       </c>
       <c r="O3" t="n">
-        <v>17.10653135535742</v>
+        <v>17.10532976668136</v>
       </c>
       <c r="P3" t="n">
-        <v>300.8841574096435</v>
+        <v>301.1624620315156</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13835,28 +13965,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.103764309753989</v>
+        <v>0.09199086652566862</v>
       </c>
       <c r="J4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00208531801139511</v>
+        <v>0.001666818564288519</v>
       </c>
       <c r="M4" t="n">
-        <v>14.39397874148137</v>
+        <v>14.27974434034173</v>
       </c>
       <c r="N4" t="n">
-        <v>331.2147956693773</v>
+        <v>327.766602659861</v>
       </c>
       <c r="O4" t="n">
-        <v>18.19930756016221</v>
+        <v>18.10432552347259</v>
       </c>
       <c r="P4" t="n">
-        <v>297.7135072954164</v>
+        <v>297.8230263398942</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13913,28 +14043,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3235791473478328</v>
+        <v>-0.3042378836696671</v>
       </c>
       <c r="J5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02302430363689112</v>
+        <v>0.02069779245051551</v>
       </c>
       <c r="M5" t="n">
-        <v>13.98544691166516</v>
+        <v>13.9508391598326</v>
       </c>
       <c r="N5" t="n">
-        <v>305.610346692228</v>
+        <v>303.4178753631317</v>
       </c>
       <c r="O5" t="n">
-        <v>17.48171463822208</v>
+        <v>17.41889420609505</v>
       </c>
       <c r="P5" t="n">
-        <v>312.5474889855243</v>
+        <v>312.3812034675652</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13991,28 +14121,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04847761325854195</v>
+        <v>-0.04361336497306474</v>
       </c>
       <c r="J6" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004171468098713715</v>
+        <v>0.0003439908888669407</v>
       </c>
       <c r="M6" t="n">
-        <v>14.5070311971788</v>
+        <v>14.37702807055872</v>
       </c>
       <c r="N6" t="n">
-        <v>351.9177773108972</v>
+        <v>347.9971761363802</v>
       </c>
       <c r="O6" t="n">
-        <v>18.75947166929008</v>
+        <v>18.6546824185345</v>
       </c>
       <c r="P6" t="n">
-        <v>330.8977476572094</v>
+        <v>330.8522270878977</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14069,28 +14199,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2063014083848329</v>
+        <v>-0.1918047360397149</v>
       </c>
       <c r="J7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00590767932871239</v>
+        <v>0.005196632623565289</v>
       </c>
       <c r="M7" t="n">
-        <v>16.50187057373014</v>
+        <v>16.38547547889587</v>
       </c>
       <c r="N7" t="n">
-        <v>413.6744021878447</v>
+        <v>409.4085167090533</v>
       </c>
       <c r="O7" t="n">
-        <v>20.33898724587448</v>
+        <v>20.23384582102605</v>
       </c>
       <c r="P7" t="n">
-        <v>350.3624569008082</v>
+        <v>350.2157948762139</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14147,28 +14277,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05307799668371324</v>
+        <v>0.05709330811643135</v>
       </c>
       <c r="J8" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004682840661146548</v>
+        <v>0.0005521948467696047</v>
       </c>
       <c r="M8" t="n">
-        <v>14.88926274632066</v>
+        <v>14.72549667965524</v>
       </c>
       <c r="N8" t="n">
-        <v>345.3955720568288</v>
+        <v>341.2315291409885</v>
       </c>
       <c r="O8" t="n">
-        <v>18.58482101223546</v>
+        <v>18.47245325182848</v>
       </c>
       <c r="P8" t="n">
-        <v>347.2738582558838</v>
+        <v>347.2332017342188</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14225,28 +14355,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01576289426815127</v>
+        <v>-0.0230920575873968</v>
       </c>
       <c r="J9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L9" t="n">
-        <v>3.644024825022463e-05</v>
+        <v>7.972078358975399e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>15.37068885713582</v>
+        <v>15.248268997164</v>
       </c>
       <c r="N9" t="n">
-        <v>411.1331606799789</v>
+        <v>406.4608479083872</v>
       </c>
       <c r="O9" t="n">
-        <v>20.27641883272238</v>
+        <v>20.1608741851237</v>
       </c>
       <c r="P9" t="n">
-        <v>353.7641724956774</v>
+        <v>353.8347410702133</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14303,28 +14433,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3614191391285288</v>
+        <v>0.3357187974984112</v>
       </c>
       <c r="J10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01966086757812291</v>
+        <v>0.01726789735491852</v>
       </c>
       <c r="M10" t="n">
-        <v>16.55040606979022</v>
+        <v>16.5604199898148</v>
       </c>
       <c r="N10" t="n">
-        <v>421.7368689451288</v>
+        <v>418.8155496173654</v>
       </c>
       <c r="O10" t="n">
-        <v>20.53623307583766</v>
+        <v>20.46498349907386</v>
       </c>
       <c r="P10" t="n">
-        <v>356.01023838266</v>
+        <v>356.2414352192933</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14381,28 +14511,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5254936545088436</v>
+        <v>0.515735712762856</v>
       </c>
       <c r="J11" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03423222277813487</v>
+        <v>0.03358919560525253</v>
       </c>
       <c r="M11" t="n">
-        <v>17.50351741482893</v>
+        <v>17.36005286261113</v>
       </c>
       <c r="N11" t="n">
-        <v>506.405213254604</v>
+        <v>501.2935890026936</v>
       </c>
       <c r="O11" t="n">
-        <v>22.50344891910136</v>
+        <v>22.38958661973672</v>
       </c>
       <c r="P11" t="n">
-        <v>357.6112549460216</v>
+        <v>357.6985538019005</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14459,28 +14589,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.386092488755517</v>
+        <v>0.3652193975384025</v>
       </c>
       <c r="J12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02323165785170855</v>
+        <v>0.02114154877724739</v>
       </c>
       <c r="M12" t="n">
-        <v>16.1320214563961</v>
+        <v>16.04681472372641</v>
       </c>
       <c r="N12" t="n">
-        <v>407.3987406339757</v>
+        <v>404.5445293820295</v>
       </c>
       <c r="O12" t="n">
-        <v>20.18412100226254</v>
+        <v>20.11329235560477</v>
       </c>
       <c r="P12" t="n">
-        <v>357.6461371955916</v>
+        <v>357.8328770869891</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -14537,28 +14667,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.255413900262378</v>
+        <v>0.2381419562790223</v>
       </c>
       <c r="J13" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0111887140469501</v>
+        <v>0.009900395467884904</v>
       </c>
       <c r="M13" t="n">
-        <v>15.10799028160361</v>
+        <v>15.02886306456274</v>
       </c>
       <c r="N13" t="n">
-        <v>381.4311813334755</v>
+        <v>378.4886622135853</v>
       </c>
       <c r="O13" t="n">
-        <v>19.53026321720922</v>
+        <v>19.4547850724079</v>
       </c>
       <c r="P13" t="n">
-        <v>355.6835629661333</v>
+        <v>355.832840397332</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -14615,28 +14745,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2127063927004595</v>
+        <v>0.1982500928705577</v>
       </c>
       <c r="J14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01019465828244026</v>
+        <v>0.009016192204835294</v>
       </c>
       <c r="M14" t="n">
-        <v>12.92153726306563</v>
+        <v>12.84979496901435</v>
       </c>
       <c r="N14" t="n">
-        <v>288.3932060447136</v>
+        <v>286.1330178232121</v>
       </c>
       <c r="O14" t="n">
-        <v>16.98214374113921</v>
+        <v>16.91546682250337</v>
       </c>
       <c r="P14" t="n">
-        <v>351.3550551549898</v>
+        <v>351.4803657368403</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -14693,28 +14823,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1847452421197394</v>
+        <v>0.1660402965270987</v>
       </c>
       <c r="J15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K15" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L15" t="n">
-        <v>0.010600055606931</v>
+        <v>0.008696303769409774</v>
       </c>
       <c r="M15" t="n">
-        <v>11.13977109939122</v>
+        <v>11.10710802217539</v>
       </c>
       <c r="N15" t="n">
-        <v>207.3653718598523</v>
+        <v>206.4267843999849</v>
       </c>
       <c r="O15" t="n">
-        <v>14.40018652170354</v>
+        <v>14.36756014081671</v>
       </c>
       <c r="P15" t="n">
-        <v>349.5903035870718</v>
+        <v>349.7530385535421</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -14771,28 +14901,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1887174916629847</v>
+        <v>0.1782300049772177</v>
       </c>
       <c r="J16" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01204627847155715</v>
+        <v>0.01094071043100964</v>
       </c>
       <c r="M16" t="n">
-        <v>10.61506612199985</v>
+        <v>10.55970870889771</v>
       </c>
       <c r="N16" t="n">
-        <v>189.4859020251795</v>
+        <v>187.9477645388548</v>
       </c>
       <c r="O16" t="n">
-        <v>13.76538782690773</v>
+        <v>13.70940423719626</v>
       </c>
       <c r="P16" t="n">
-        <v>344.5959717702686</v>
+        <v>344.6877573235585</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -14849,28 +14979,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.119224113771397</v>
+        <v>0.1023799086502922</v>
       </c>
       <c r="J17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K17" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004409414623288366</v>
+        <v>0.003302538195074645</v>
       </c>
       <c r="M17" t="n">
-        <v>11.23367286484208</v>
+        <v>11.21661012790294</v>
       </c>
       <c r="N17" t="n">
-        <v>199.9150100491622</v>
+        <v>198.8789409504565</v>
       </c>
       <c r="O17" t="n">
-        <v>14.13913045590719</v>
+        <v>14.10244450265473</v>
       </c>
       <c r="P17" t="n">
-        <v>342.6527483023974</v>
+        <v>342.804215749847</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -14927,28 +15057,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03747910443960157</v>
+        <v>-0.02451249721641745</v>
       </c>
       <c r="J18" t="n">
+        <v>104</v>
+      </c>
+      <c r="K18" t="n">
         <v>103</v>
       </c>
-      <c r="K18" t="n">
-        <v>102</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0003832276823172442</v>
+        <v>0.000171884791979493</v>
       </c>
       <c r="M18" t="n">
-        <v>12.34234152850231</v>
+        <v>12.01308999934153</v>
       </c>
       <c r="N18" t="n">
-        <v>235.057367747627</v>
+        <v>226.2134577627738</v>
       </c>
       <c r="O18" t="n">
-        <v>15.33158073218893</v>
+        <v>15.04039420237295</v>
       </c>
       <c r="P18" t="n">
-        <v>336.8610453602001</v>
+        <v>337.3965550542962</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15005,28 +15135,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1207035871101125</v>
+        <v>0.1083386155508192</v>
       </c>
       <c r="J19" t="n">
+        <v>104</v>
+      </c>
+      <c r="K19" t="n">
         <v>103</v>
       </c>
-      <c r="K19" t="n">
-        <v>102</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.003936833428121456</v>
+        <v>0.003226796078864225</v>
       </c>
       <c r="M19" t="n">
-        <v>11.90908237048089</v>
+        <v>11.86315495234774</v>
       </c>
       <c r="N19" t="n">
-        <v>228.9041825658946</v>
+        <v>227.18717643143</v>
       </c>
       <c r="O19" t="n">
-        <v>15.12957972205093</v>
+        <v>15.0727295614109</v>
       </c>
       <c r="P19" t="n">
-        <v>332.117307344602</v>
+        <v>332.2291017642745</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15083,28 +15213,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1467677142230734</v>
+        <v>0.1381805861695443</v>
       </c>
       <c r="J20" t="n">
+        <v>104</v>
+      </c>
+      <c r="K20" t="n">
         <v>103</v>
       </c>
-      <c r="K20" t="n">
-        <v>102</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.00507334521294267</v>
+        <v>0.004580271707896877</v>
       </c>
       <c r="M20" t="n">
-        <v>13.55389662455396</v>
+        <v>13.47259931882399</v>
       </c>
       <c r="N20" t="n">
-        <v>262.3199048896378</v>
+        <v>260.0168427482679</v>
       </c>
       <c r="O20" t="n">
-        <v>16.19629293664565</v>
+        <v>16.125037759592</v>
       </c>
       <c r="P20" t="n">
-        <v>325.321685791543</v>
+        <v>325.3993238995479</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -15161,28 +15291,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2784507499751508</v>
+        <v>0.2759214361671072</v>
       </c>
       <c r="J21" t="n">
+        <v>104</v>
+      </c>
+      <c r="K21" t="n">
         <v>103</v>
       </c>
-      <c r="K21" t="n">
-        <v>102</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.01810116268915818</v>
+        <v>0.0181091255772684</v>
       </c>
       <c r="M21" t="n">
-        <v>13.50294423992717</v>
+        <v>13.38593959474873</v>
       </c>
       <c r="N21" t="n">
-        <v>261.1743915623297</v>
+        <v>258.6598636508934</v>
       </c>
       <c r="O21" t="n">
-        <v>16.16089080349006</v>
+        <v>16.08290594547184</v>
       </c>
       <c r="P21" t="n">
-        <v>317.1130638721489</v>
+        <v>317.135931953</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -15239,28 +15369,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2620740843987464</v>
+        <v>0.2696231943943513</v>
       </c>
       <c r="J22" t="n">
+        <v>104</v>
+      </c>
+      <c r="K22" t="n">
         <v>103</v>
       </c>
-      <c r="K22" t="n">
-        <v>102</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01813886132484022</v>
+        <v>0.01951927198527137</v>
       </c>
       <c r="M22" t="n">
-        <v>12.5784249298272</v>
+        <v>12.4983151284113</v>
       </c>
       <c r="N22" t="n">
-        <v>230.8669358402674</v>
+        <v>228.8138785486009</v>
       </c>
       <c r="O22" t="n">
-        <v>15.19430603352017</v>
+        <v>15.12659507452358</v>
       </c>
       <c r="P22" t="n">
-        <v>311.5253897371156</v>
+        <v>311.4571365780238</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -15317,28 +15447,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.07868462268206709</v>
+        <v>0.0887160833177303</v>
       </c>
       <c r="J23" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K23" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001770176600128237</v>
+        <v>0.0022887227721895</v>
       </c>
       <c r="M23" t="n">
-        <v>11.70930565490992</v>
+        <v>11.65670745030912</v>
       </c>
       <c r="N23" t="n">
-        <v>220.4509803868156</v>
+        <v>218.624356458629</v>
       </c>
       <c r="O23" t="n">
-        <v>14.84759173693888</v>
+        <v>14.78595132071755</v>
       </c>
       <c r="P23" t="n">
-        <v>308.3577215654806</v>
+        <v>308.2684487122552</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -15395,28 +15525,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1163945779596177</v>
+        <v>0.1308918698128325</v>
       </c>
       <c r="J24" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K24" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002895984238455829</v>
+        <v>0.003721544199854265</v>
       </c>
       <c r="M24" t="n">
-        <v>13.64185948812728</v>
+        <v>13.59297801994982</v>
       </c>
       <c r="N24" t="n">
-        <v>281.4511738611255</v>
+        <v>279.295714450355</v>
       </c>
       <c r="O24" t="n">
-        <v>16.77650660480678</v>
+        <v>16.71214272468839</v>
       </c>
       <c r="P24" t="n">
-        <v>302.5116482532746</v>
+        <v>302.3769223550178</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -15473,28 +15603,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08671835799024756</v>
+        <v>0.09446608745814138</v>
       </c>
       <c r="J25" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K25" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001645215280142942</v>
+        <v>0.001988162589036224</v>
       </c>
       <c r="M25" t="n">
-        <v>13.61481007320998</v>
+        <v>13.52572078750945</v>
       </c>
       <c r="N25" t="n">
-        <v>278.6089767905727</v>
+        <v>276.041052831702</v>
       </c>
       <c r="O25" t="n">
-        <v>16.69158401082931</v>
+        <v>16.61448322493667</v>
       </c>
       <c r="P25" t="n">
-        <v>297.6135707640751</v>
+        <v>297.5425148186208</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -15551,28 +15681,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4438096428716601</v>
+        <v>0.482677847484106</v>
       </c>
       <c r="J26" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K26" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02539333393068921</v>
+        <v>0.03015999939238823</v>
       </c>
       <c r="M26" t="n">
-        <v>17.71198381925604</v>
+        <v>17.78314032719759</v>
       </c>
       <c r="N26" t="n">
-        <v>459.9714182295092</v>
+        <v>460.0655395468189</v>
       </c>
       <c r="O26" t="n">
-        <v>21.44694426321636</v>
+        <v>21.44913843367185</v>
       </c>
       <c r="P26" t="n">
-        <v>283.5522780042766</v>
+        <v>283.1935106081639</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -15629,28 +15759,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1839308393722468</v>
+        <v>0.2303301867695402</v>
       </c>
       <c r="J27" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K27" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005352909862827882</v>
+        <v>0.008439415091780478</v>
       </c>
       <c r="M27" t="n">
-        <v>15.6140650365621</v>
+        <v>15.68259486298028</v>
       </c>
       <c r="N27" t="n">
-        <v>391.1302497568333</v>
+        <v>391.3184632443149</v>
       </c>
       <c r="O27" t="n">
-        <v>19.77701316571421</v>
+        <v>19.781770983517</v>
       </c>
       <c r="P27" t="n">
-        <v>284.4691421725686</v>
+        <v>284.0506333961511</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -15707,28 +15837,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2442665459370536</v>
+        <v>-0.2162406847023543</v>
       </c>
       <c r="J28" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K28" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01372460372301765</v>
+        <v>0.01089312982581236</v>
       </c>
       <c r="M28" t="n">
-        <v>12.95296631705948</v>
+        <v>12.9437519095885</v>
       </c>
       <c r="N28" t="n">
-        <v>256.314398810304</v>
+        <v>256.1789334057332</v>
       </c>
       <c r="O28" t="n">
-        <v>16.00982194811372</v>
+        <v>16.00559069218419</v>
       </c>
       <c r="P28" t="n">
-        <v>291.1607501521986</v>
+        <v>290.8985489319181</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -15785,28 +15915,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1467325097143536</v>
+        <v>-0.1305651459524657</v>
       </c>
       <c r="J29" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K29" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L29" t="n">
-        <v>0.005385545754436838</v>
+        <v>0.004333559725336777</v>
       </c>
       <c r="M29" t="n">
-        <v>13.08832055548527</v>
+        <v>13.05630765559686</v>
       </c>
       <c r="N29" t="n">
-        <v>252.7592167203202</v>
+        <v>251.2197125327351</v>
       </c>
       <c r="O29" t="n">
-        <v>15.89840296131408</v>
+        <v>15.84991206703479</v>
       </c>
       <c r="P29" t="n">
-        <v>287.2471248262469</v>
+        <v>287.1042210254374</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -15863,28 +15993,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09740942054641286</v>
+        <v>0.1053350672548417</v>
       </c>
       <c r="J30" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K30" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L30" t="n">
-        <v>0.002800502211106282</v>
+        <v>0.003331262037826743</v>
       </c>
       <c r="M30" t="n">
-        <v>11.62444515073203</v>
+        <v>11.55662680175521</v>
       </c>
       <c r="N30" t="n">
-        <v>214.7718281385035</v>
+        <v>212.9208095150366</v>
       </c>
       <c r="O30" t="n">
-        <v>14.65509563730321</v>
+        <v>14.59180624580235</v>
       </c>
       <c r="P30" t="n">
-        <v>283.1114253180797</v>
+        <v>283.0413702951836</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -15941,28 +16071,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07380317652694852</v>
+        <v>0.07754843061168271</v>
       </c>
       <c r="J31" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K31" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L31" t="n">
-        <v>0.001450933837587876</v>
+        <v>0.001631450885759</v>
       </c>
       <c r="M31" t="n">
-        <v>11.91625173414822</v>
+        <v>11.82446688535756</v>
       </c>
       <c r="N31" t="n">
-        <v>238.2874515554264</v>
+        <v>236.0440339852032</v>
       </c>
       <c r="O31" t="n">
-        <v>15.43656216764039</v>
+        <v>15.36372461303584</v>
       </c>
       <c r="P31" t="n">
-        <v>281.8955964547229</v>
+        <v>281.8624920444066</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16019,28 +16149,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.04815647194218988</v>
+        <v>-0.0515053203545527</v>
       </c>
       <c r="J32" t="n">
+        <v>104</v>
+      </c>
+      <c r="K32" t="n">
         <v>103</v>
       </c>
-      <c r="K32" t="n">
-        <v>102</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0005217393859282549</v>
+        <v>0.0006079742728827275</v>
       </c>
       <c r="M32" t="n">
-        <v>13.22159481819538</v>
+        <v>13.11044628362825</v>
       </c>
       <c r="N32" t="n">
-        <v>277.1613869239571</v>
+        <v>274.507845027855</v>
       </c>
       <c r="O32" t="n">
-        <v>16.64816467133711</v>
+        <v>16.56827827590589</v>
       </c>
       <c r="P32" t="n">
-        <v>286.2699688480514</v>
+        <v>286.3001413035243</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -16097,28 +16227,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4086554585787787</v>
+        <v>-0.4063196204502716</v>
       </c>
       <c r="J33" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K33" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03954127467430801</v>
+        <v>0.03982106508737482</v>
       </c>
       <c r="M33" t="n">
-        <v>12.5069046880058</v>
+        <v>12.39996795326242</v>
       </c>
       <c r="N33" t="n">
-        <v>246.8496793944558</v>
+        <v>244.447164278253</v>
       </c>
       <c r="O33" t="n">
-        <v>15.71145058212181</v>
+        <v>15.63480617974694</v>
       </c>
       <c r="P33" t="n">
-        <v>303.5540496403081</v>
+        <v>303.5325119977599</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -16175,28 +16305,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1585952245979589</v>
+        <v>-0.1515103734536694</v>
       </c>
       <c r="J34" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K34" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L34" t="n">
-        <v>0.006503905767941021</v>
+        <v>0.006047223779479083</v>
       </c>
       <c r="M34" t="n">
-        <v>12.59763205202547</v>
+        <v>12.51983266768856</v>
       </c>
       <c r="N34" t="n">
-        <v>240.8511205338368</v>
+        <v>238.6567862174474</v>
       </c>
       <c r="O34" t="n">
-        <v>15.51937887074856</v>
+        <v>15.44852051872435</v>
       </c>
       <c r="P34" t="n">
-        <v>311.031711784454</v>
+        <v>310.9680894086845</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -16253,28 +16383,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1645271059641714</v>
+        <v>-0.1457034442946467</v>
       </c>
       <c r="J35" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K35" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>0.006312383486350437</v>
+        <v>0.005028381847972274</v>
       </c>
       <c r="M35" t="n">
-        <v>13.60597881776805</v>
+        <v>13.6017580182417</v>
       </c>
       <c r="N35" t="n">
-        <v>266.5611852766762</v>
+        <v>265.0761973224592</v>
       </c>
       <c r="O35" t="n">
-        <v>16.32670160432524</v>
+        <v>16.28116081004236</v>
       </c>
       <c r="P35" t="n">
-        <v>319.0370485734146</v>
+        <v>318.8665001921091</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -16331,28 +16461,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2309708411233952</v>
+        <v>-0.1956508782422649</v>
       </c>
       <c r="J36" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K36" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0153216096937554</v>
+        <v>0.01110155887440223</v>
       </c>
       <c r="M36" t="n">
-        <v>12.82092674183401</v>
+        <v>12.95619906929464</v>
       </c>
       <c r="N36" t="n">
-        <v>217.1925665822714</v>
+        <v>217.9131978097725</v>
       </c>
       <c r="O36" t="n">
-        <v>14.73745454894676</v>
+        <v>14.76188327449355</v>
       </c>
       <c r="P36" t="n">
-        <v>335.8868703899892</v>
+        <v>335.5726284348081</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -16409,28 +16539,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1300277996597122</v>
+        <v>-0.1167502964500247</v>
       </c>
       <c r="J37" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K37" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L37" t="n">
-        <v>0.005538509449693141</v>
+        <v>0.004541526691140718</v>
       </c>
       <c r="M37" t="n">
-        <v>11.83057647162332</v>
+        <v>11.79718787712932</v>
       </c>
       <c r="N37" t="n">
-        <v>192.3127727205286</v>
+        <v>190.936723314045</v>
       </c>
       <c r="O37" t="n">
-        <v>13.86768808131077</v>
+        <v>13.81798550129667</v>
       </c>
       <c r="P37" t="n">
-        <v>330.3286129220675</v>
+        <v>330.209516339283</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -16468,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL104"/>
+  <dimension ref="A1:AL105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35051,7 +35181,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>-34.49402662164972,173.0021420592918</t>
+          <t>-34.494040330139306,173.00202966784633</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -35243,7 +35373,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>-34.49401397767793,173.00224572231818</t>
+          <t>-34.4940408558703,173.0020253575313</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -35288,7 +35418,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>-34.50070447091792,173.00290817675645</t>
+          <t>-34.500685554027285,173.00301802282115</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
@@ -35333,7 +35463,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>-34.50720788090892,173.00451212429712</t>
+          <t>-34.507190719066216,173.0046066137101</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -35342,6 +35472,198 @@
         </is>
       </c>
       <c r="AL104" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-34.48232233028089,173.00269650847892</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>-34.48293775155903,173.00218491420148</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>-34.48363025462321,173.00185359529308</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-34.484376420272646,173.00164778516285</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-34.48512446157427,173.0013889796995</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-34.485905267645016,173.00130158671752</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-34.48666017277562,173.00124536580395</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-34.487399764697685,173.0012007633868</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-34.48814493980412,173.00119241239005</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>-34.48888093213282,173.00137762708982</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-34.48962621198505,173.00140127106732</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>-34.49036307093825,173.00149652272486</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>-34.491100501790875,173.00158703257856</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>-34.49183946399299,173.00166493438354</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>-34.49257216368063,173.0017941271271</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>-34.49331433317784,173.00184562707616</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>-34.49405422252995,173.00191576775333</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>-34.49479207287064,173.0020224548269</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>-34.49553234160182,173.00212536513638</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>-34.496265517440754,173.00226384483253</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>-34.49699533251341,173.00241488620557</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>-34.49773482757642,173.00249742491624</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>-34.49846955955047,173.00262153278263</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>-34.49922281089412,173.00267799523183</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>-34.49993265793289,173.00299817942403</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>-34.500677675021365,173.0030637742257</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>-34.501411996892045,173.00319143586955</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>-34.50215044491415,173.00329510066106</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>-34.50288040157823,173.0034480361089</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>-34.503606300534216,173.00358316543972</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>-34.504288277545484,173.00370672590225</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>-34.50497675969308,173.00388591133864</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>-34.50570514902972,173.00412851728174</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>-34.50643477432047,173.0043489540084</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>-34.50719398523334,173.00458863093064</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>-34.50793519368222,173.00484749860968</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL105"/>
+  <dimension ref="A1:AL106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12557,6 +12557,126 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>305.89</v>
+      </c>
+      <c r="C106" t="n">
+        <v>305.73</v>
+      </c>
+      <c r="D106" t="n">
+        <v>314.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>321.32</v>
+      </c>
+      <c r="F106" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="G106" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="H106" t="n">
+        <v>361</v>
+      </c>
+      <c r="I106" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="J106" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="K106" t="n">
+        <v>377.71</v>
+      </c>
+      <c r="L106" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="M106" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="N106" t="n">
+        <v>356.37</v>
+      </c>
+      <c r="O106" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="P106" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="R106" t="n">
+        <v>346.05</v>
+      </c>
+      <c r="S106" t="n">
+        <v>335.05</v>
+      </c>
+      <c r="T106" t="n">
+        <v>331.09</v>
+      </c>
+      <c r="U106" t="n">
+        <v>334.02</v>
+      </c>
+      <c r="V106" t="n">
+        <v>331.38</v>
+      </c>
+      <c r="W106" t="n">
+        <v>325.22</v>
+      </c>
+      <c r="X106" t="n">
+        <v>323.77</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>312.48</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>312.21</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>313.81</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>306</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>298.39</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>299</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>293.73</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>292.29</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>304.94</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>351.84</v>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12568,7 +12688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13641,6 +13761,16 @@
       </c>
       <c r="B107" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13809,28 +13939,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04203941097004492</v>
+        <v>-0.04618297019732825</v>
       </c>
       <c r="J2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004724080594854518</v>
+        <v>0.0005807814672931233</v>
       </c>
       <c r="M2" t="n">
-        <v>13.5828062174127</v>
+        <v>13.44804019717085</v>
       </c>
       <c r="N2" t="n">
-        <v>252.7672320770698</v>
+        <v>249.8548296156929</v>
       </c>
       <c r="O2" t="n">
-        <v>15.89865503987899</v>
+        <v>15.80679694358389</v>
       </c>
       <c r="P2" t="n">
-        <v>309.2991375900362</v>
+        <v>309.3360124671183</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13887,28 +14017,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03943518791290231</v>
+        <v>0.04564624307182264</v>
       </c>
       <c r="J3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003519537109034632</v>
+        <v>0.0004797798055559133</v>
       </c>
       <c r="M3" t="n">
-        <v>13.60583811903392</v>
+        <v>13.49128795502531</v>
       </c>
       <c r="N3" t="n">
-        <v>292.5923064269153</v>
+        <v>289.3322693197931</v>
       </c>
       <c r="O3" t="n">
-        <v>17.10532976668136</v>
+        <v>17.00976981971811</v>
       </c>
       <c r="P3" t="n">
-        <v>301.1624620315156</v>
+        <v>301.105648129486</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13965,28 +14095,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09199086652566862</v>
+        <v>0.1165898360809265</v>
       </c>
       <c r="J4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001666818564288519</v>
+        <v>0.00270397489876717</v>
       </c>
       <c r="M4" t="n">
-        <v>14.27974434034173</v>
+        <v>14.31407139277526</v>
       </c>
       <c r="N4" t="n">
-        <v>327.766602659861</v>
+        <v>326.1163358295815</v>
       </c>
       <c r="O4" t="n">
-        <v>18.10432552347259</v>
+        <v>18.05869142074202</v>
       </c>
       <c r="P4" t="n">
-        <v>297.8230263398942</v>
+        <v>297.5920415460967</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14043,28 +14173,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3042378836696671</v>
+        <v>-0.2751777182577507</v>
       </c>
       <c r="J5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02069779245051551</v>
+        <v>0.01713250147251699</v>
       </c>
       <c r="M5" t="n">
-        <v>13.9508391598326</v>
+        <v>13.97821186416537</v>
       </c>
       <c r="N5" t="n">
-        <v>303.4178753631317</v>
+        <v>303.0783418755996</v>
       </c>
       <c r="O5" t="n">
-        <v>17.41889420609505</v>
+        <v>17.40914535167076</v>
       </c>
       <c r="P5" t="n">
-        <v>312.3812034675652</v>
+        <v>312.1289854029188</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14121,28 +14251,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04361336497306474</v>
+        <v>-0.01680347350527462</v>
       </c>
       <c r="J6" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003439908888669407</v>
+        <v>5.166626335317837e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>14.37702807055872</v>
+        <v>14.40318935542138</v>
       </c>
       <c r="N6" t="n">
-        <v>347.9971761363802</v>
+        <v>346.525899998411</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6546824185345</v>
+        <v>18.61520614976936</v>
       </c>
       <c r="P6" t="n">
-        <v>330.8522270878977</v>
+        <v>330.5991891755737</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14199,28 +14329,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1918047360397149</v>
+        <v>-0.1609177012347066</v>
       </c>
       <c r="J7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005196632623565289</v>
+        <v>0.003702245529263459</v>
       </c>
       <c r="M7" t="n">
-        <v>16.38547547889587</v>
+        <v>16.35883675184305</v>
       </c>
       <c r="N7" t="n">
-        <v>409.4085167090533</v>
+        <v>407.6449662258716</v>
       </c>
       <c r="O7" t="n">
-        <v>20.23384582102605</v>
+        <v>20.1902195685404</v>
       </c>
       <c r="P7" t="n">
-        <v>350.2157948762139</v>
+        <v>349.9006634686467</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14277,28 +14407,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05709330811643135</v>
+        <v>0.08114159991952113</v>
       </c>
       <c r="J8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005521948467696047</v>
+        <v>0.001130052977578844</v>
       </c>
       <c r="M8" t="n">
-        <v>14.72549667965524</v>
+        <v>14.65166053167122</v>
       </c>
       <c r="N8" t="n">
-        <v>341.2315291409885</v>
+        <v>338.8852308544656</v>
       </c>
       <c r="O8" t="n">
-        <v>18.47245325182848</v>
+        <v>18.40883567351465</v>
       </c>
       <c r="P8" t="n">
-        <v>347.2332017342188</v>
+        <v>346.9876805169342</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14355,28 +14485,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0230920575873968</v>
+        <v>-0.00810996308104673</v>
       </c>
       <c r="J9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L9" t="n">
-        <v>7.972078358975399e-05</v>
+        <v>1.000788978555711e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>15.248268997164</v>
+        <v>15.13253441003714</v>
       </c>
       <c r="N9" t="n">
-        <v>406.4608479083872</v>
+        <v>402.4392673366731</v>
       </c>
       <c r="O9" t="n">
-        <v>20.1608741851237</v>
+        <v>20.06088899666894</v>
       </c>
       <c r="P9" t="n">
-        <v>353.8347410702133</v>
+        <v>353.6892972932565</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14433,28 +14563,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3357187974984112</v>
+        <v>0.3429555287676729</v>
       </c>
       <c r="J10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01726789735491852</v>
+        <v>0.01835561644411599</v>
       </c>
       <c r="M10" t="n">
-        <v>16.5604199898148</v>
+        <v>16.39686473200792</v>
       </c>
       <c r="N10" t="n">
-        <v>418.8155496173654</v>
+        <v>414.0593610406795</v>
       </c>
       <c r="O10" t="n">
-        <v>20.46498349907386</v>
+        <v>20.34844861508315</v>
       </c>
       <c r="P10" t="n">
-        <v>356.2414352192933</v>
+        <v>356.1757724062599</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14511,28 +14641,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.515735712762856</v>
+        <v>0.5271017147644137</v>
       </c>
       <c r="J11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03358919560525253</v>
+        <v>0.03562365155173974</v>
       </c>
       <c r="M11" t="n">
-        <v>17.36005286261113</v>
+        <v>17.26288158509902</v>
       </c>
       <c r="N11" t="n">
-        <v>501.2935890026936</v>
+        <v>496.4236933258694</v>
       </c>
       <c r="O11" t="n">
-        <v>22.38958661973672</v>
+        <v>22.28056761677919</v>
       </c>
       <c r="P11" t="n">
-        <v>357.6985538019005</v>
+        <v>357.5959948578507</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14589,28 +14719,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3652193975384025</v>
+        <v>0.3659935804822679</v>
       </c>
       <c r="J12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02114154877724739</v>
+        <v>0.02161174987339998</v>
       </c>
       <c r="M12" t="n">
-        <v>16.04681472372641</v>
+        <v>15.88233953785661</v>
       </c>
       <c r="N12" t="n">
-        <v>404.5445293820295</v>
+        <v>400.2430123359921</v>
       </c>
       <c r="O12" t="n">
-        <v>20.11329235560477</v>
+        <v>20.00607438594569</v>
       </c>
       <c r="P12" t="n">
-        <v>357.8328770869891</v>
+        <v>357.8258913953438</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -14667,28 +14797,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2381419562790223</v>
+        <v>0.2349428755232988</v>
       </c>
       <c r="J13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009900395467884904</v>
+        <v>0.009819189118107086</v>
       </c>
       <c r="M13" t="n">
-        <v>15.02886306456274</v>
+        <v>14.88806522115565</v>
       </c>
       <c r="N13" t="n">
-        <v>378.4886622135853</v>
+        <v>374.622957397246</v>
       </c>
       <c r="O13" t="n">
-        <v>19.4547850724079</v>
+        <v>19.35517908460797</v>
       </c>
       <c r="P13" t="n">
-        <v>355.832840397332</v>
+        <v>355.8607200903468</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -14745,28 +14875,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1982500928705577</v>
+        <v>0.1978631358954287</v>
       </c>
       <c r="J14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009016192204835294</v>
+        <v>0.00915135427301117</v>
       </c>
       <c r="M14" t="n">
-        <v>12.84979496901435</v>
+        <v>12.72028076118065</v>
       </c>
       <c r="N14" t="n">
-        <v>286.1330178232121</v>
+        <v>283.2138167796413</v>
       </c>
       <c r="O14" t="n">
-        <v>16.91546682250337</v>
+        <v>16.82895768547896</v>
       </c>
       <c r="P14" t="n">
-        <v>351.4803657368403</v>
+        <v>351.4837474541114</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -14823,28 +14953,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1660402965270987</v>
+        <v>0.1629025642815511</v>
       </c>
       <c r="J15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K15" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L15" t="n">
-        <v>0.008696303769409774</v>
+        <v>0.008531516925105342</v>
       </c>
       <c r="M15" t="n">
-        <v>11.10710802217539</v>
+        <v>11.00818057226277</v>
       </c>
       <c r="N15" t="n">
-        <v>206.4267843999849</v>
+        <v>204.3756338382291</v>
       </c>
       <c r="O15" t="n">
-        <v>14.36756014081671</v>
+        <v>14.2960006238888</v>
       </c>
       <c r="P15" t="n">
-        <v>349.7530385535421</v>
+        <v>349.7805565776424</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -14901,28 +15031,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1782300049772177</v>
+        <v>0.1880263081471053</v>
       </c>
       <c r="J16" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01094071043100964</v>
+        <v>0.01236590571508989</v>
       </c>
       <c r="M16" t="n">
-        <v>10.55970870889771</v>
+        <v>10.5209792453898</v>
       </c>
       <c r="N16" t="n">
-        <v>187.9477645388548</v>
+        <v>186.4042073867623</v>
       </c>
       <c r="O16" t="n">
-        <v>13.70940423719626</v>
+        <v>13.65299261652046</v>
       </c>
       <c r="P16" t="n">
-        <v>344.6877573235585</v>
+        <v>344.6013301592504</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -14979,28 +15109,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1023799086502922</v>
+        <v>0.1016656341218573</v>
       </c>
       <c r="J17" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K17" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003302538195074645</v>
+        <v>0.003318482497371211</v>
       </c>
       <c r="M17" t="n">
-        <v>11.21661012790294</v>
+        <v>11.11157510263244</v>
       </c>
       <c r="N17" t="n">
-        <v>198.8789409504565</v>
+        <v>196.9497790838796</v>
       </c>
       <c r="O17" t="n">
-        <v>14.10244450265473</v>
+        <v>14.03387968752332</v>
       </c>
       <c r="P17" t="n">
-        <v>342.804215749847</v>
+        <v>342.8106871750954</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -15057,28 +15187,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02451249721641745</v>
+        <v>-0.009397708278787029</v>
       </c>
       <c r="J18" t="n">
+        <v>105</v>
+      </c>
+      <c r="K18" t="n">
         <v>104</v>
       </c>
-      <c r="K18" t="n">
-        <v>103</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.000171884791979493</v>
+        <v>2.564304108187976e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>12.01308999934153</v>
+        <v>11.9792913791505</v>
       </c>
       <c r="N18" t="n">
-        <v>226.2134577627738</v>
+        <v>224.8446516064881</v>
       </c>
       <c r="O18" t="n">
-        <v>15.04039420237295</v>
+        <v>14.99482082608819</v>
       </c>
       <c r="P18" t="n">
-        <v>337.3965550542962</v>
+        <v>337.2625673972888</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15135,28 +15265,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1083386155508192</v>
+        <v>0.1083689146267544</v>
       </c>
       <c r="J19" t="n">
+        <v>105</v>
+      </c>
+      <c r="K19" t="n">
         <v>104</v>
       </c>
-      <c r="K19" t="n">
-        <v>103</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.003226796078864225</v>
+        <v>0.003288736673437986</v>
       </c>
       <c r="M19" t="n">
-        <v>11.86315495234774</v>
+        <v>11.7492597301354</v>
       </c>
       <c r="N19" t="n">
-        <v>227.18717643143</v>
+        <v>225.0026874556807</v>
       </c>
       <c r="O19" t="n">
-        <v>15.0727295614109</v>
+        <v>15.00008958158853</v>
       </c>
       <c r="P19" t="n">
-        <v>332.2291017642745</v>
+        <v>332.228825750396</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15213,28 +15343,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1381805861695443</v>
+        <v>0.1417005627394742</v>
       </c>
       <c r="J20" t="n">
+        <v>105</v>
+      </c>
+      <c r="K20" t="n">
         <v>104</v>
       </c>
-      <c r="K20" t="n">
-        <v>103</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.004580271707896877</v>
+        <v>0.004904220469117315</v>
       </c>
       <c r="M20" t="n">
-        <v>13.47259931882399</v>
+        <v>13.36246092380628</v>
       </c>
       <c r="N20" t="n">
-        <v>260.0168427482679</v>
+        <v>257.5585917421552</v>
       </c>
       <c r="O20" t="n">
-        <v>16.125037759592</v>
+        <v>16.04863208320744</v>
       </c>
       <c r="P20" t="n">
-        <v>325.3993238995479</v>
+        <v>325.3672581564446</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -15291,28 +15421,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2759214361671072</v>
+        <v>0.292144710199417</v>
       </c>
       <c r="J21" t="n">
+        <v>105</v>
+      </c>
+      <c r="K21" t="n">
         <v>104</v>
       </c>
-      <c r="K21" t="n">
-        <v>103</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.0181091255772684</v>
+        <v>0.02055764269448446</v>
       </c>
       <c r="M21" t="n">
-        <v>13.38593959474873</v>
+        <v>13.35123375136314</v>
       </c>
       <c r="N21" t="n">
-        <v>258.6598636508934</v>
+        <v>257.0630260560208</v>
       </c>
       <c r="O21" t="n">
-        <v>16.08290594547184</v>
+        <v>16.03318515005739</v>
       </c>
       <c r="P21" t="n">
-        <v>317.135931953</v>
+        <v>316.9881436575157</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -15369,28 +15499,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2696231943943513</v>
+        <v>0.291168598719825</v>
       </c>
       <c r="J22" t="n">
+        <v>105</v>
+      </c>
+      <c r="K22" t="n">
         <v>104</v>
       </c>
-      <c r="K22" t="n">
-        <v>103</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01951927198527137</v>
+        <v>0.02294876425759651</v>
       </c>
       <c r="M22" t="n">
-        <v>12.4983151284113</v>
+        <v>12.4953837516514</v>
       </c>
       <c r="N22" t="n">
-        <v>228.8138785486009</v>
+        <v>228.1839531107526</v>
       </c>
       <c r="O22" t="n">
-        <v>15.12659507452358</v>
+        <v>15.10575893858871</v>
       </c>
       <c r="P22" t="n">
-        <v>311.4571365780238</v>
+        <v>311.2608655556371</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -15447,28 +15577,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0887160833177303</v>
+        <v>0.113119553696978</v>
       </c>
       <c r="J23" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K23" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0022887227721895</v>
+        <v>0.003750592164399325</v>
       </c>
       <c r="M23" t="n">
-        <v>11.65670745030912</v>
+        <v>11.6927138458107</v>
       </c>
       <c r="N23" t="n">
-        <v>218.624356458629</v>
+        <v>218.5299715937845</v>
       </c>
       <c r="O23" t="n">
-        <v>14.78595132071755</v>
+        <v>14.78275926861371</v>
       </c>
       <c r="P23" t="n">
-        <v>308.2684487122552</v>
+        <v>308.0496061987427</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -15525,28 +15655,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1308918698128325</v>
+        <v>0.1620603071842592</v>
       </c>
       <c r="J24" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003721544199854265</v>
+        <v>0.005737595396035911</v>
       </c>
       <c r="M24" t="n">
-        <v>13.59297801994982</v>
+        <v>13.65206844209169</v>
       </c>
       <c r="N24" t="n">
-        <v>279.295714450355</v>
+        <v>279.6502904373605</v>
       </c>
       <c r="O24" t="n">
-        <v>16.71214272468839</v>
+        <v>16.72274769400533</v>
       </c>
       <c r="P24" t="n">
-        <v>302.3769223550178</v>
+        <v>302.0851229205801</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -15603,28 +15733,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09446608745814138</v>
+        <v>0.115850535626856</v>
       </c>
       <c r="J25" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K25" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001988162589036224</v>
+        <v>0.003027702986857395</v>
       </c>
       <c r="M25" t="n">
-        <v>13.52572078750945</v>
+        <v>13.51644353295141</v>
       </c>
       <c r="N25" t="n">
-        <v>276.041052831702</v>
+        <v>274.8218933730634</v>
       </c>
       <c r="O25" t="n">
-        <v>16.61448322493667</v>
+        <v>16.57775296513564</v>
       </c>
       <c r="P25" t="n">
-        <v>297.5425148186208</v>
+        <v>297.3449355348445</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -15681,28 +15811,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.482677847484106</v>
+        <v>0.5114475795754879</v>
       </c>
       <c r="J26" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03015999939238823</v>
+        <v>0.03417271142528</v>
       </c>
       <c r="M26" t="n">
-        <v>17.78314032719759</v>
+        <v>17.78640871346768</v>
       </c>
       <c r="N26" t="n">
-        <v>460.0655395468189</v>
+        <v>458.1259176046777</v>
       </c>
       <c r="O26" t="n">
-        <v>21.44913843367185</v>
+        <v>21.4038762284937</v>
       </c>
       <c r="P26" t="n">
-        <v>283.1935106081639</v>
+        <v>282.9259701662417</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -15759,28 +15889,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2303301867695402</v>
+        <v>0.2709881193678548</v>
       </c>
       <c r="J27" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K27" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>0.008439415091780478</v>
+        <v>0.01169829176073034</v>
       </c>
       <c r="M27" t="n">
-        <v>15.68259486298028</v>
+        <v>15.71725298786471</v>
       </c>
       <c r="N27" t="n">
-        <v>391.3184632443149</v>
+        <v>392.9153121019764</v>
       </c>
       <c r="O27" t="n">
-        <v>19.781770983517</v>
+        <v>19.8220915168399</v>
       </c>
       <c r="P27" t="n">
-        <v>284.0506333961511</v>
+        <v>283.6784726055903</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -15837,28 +15967,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2162406847023543</v>
+        <v>-0.1801862236772125</v>
       </c>
       <c r="J28" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01089312982581236</v>
+        <v>0.007611020220840148</v>
       </c>
       <c r="M28" t="n">
-        <v>12.9437519095885</v>
+        <v>12.96679193607639</v>
       </c>
       <c r="N28" t="n">
-        <v>256.1789334057332</v>
+        <v>257.7579559420625</v>
       </c>
       <c r="O28" t="n">
-        <v>16.00559069218419</v>
+        <v>16.05484213382562</v>
       </c>
       <c r="P28" t="n">
-        <v>290.8985489319181</v>
+        <v>290.5587654021401</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -15915,28 +16045,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1305651459524657</v>
+        <v>-0.1066857554180887</v>
       </c>
       <c r="J29" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K29" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L29" t="n">
-        <v>0.004333559725336777</v>
+        <v>0.002927805215094281</v>
       </c>
       <c r="M29" t="n">
-        <v>13.05630765559686</v>
+        <v>13.06750055254265</v>
       </c>
       <c r="N29" t="n">
-        <v>251.2197125327351</v>
+        <v>250.8159312237903</v>
       </c>
       <c r="O29" t="n">
-        <v>15.84991206703479</v>
+        <v>15.83716929327303</v>
       </c>
       <c r="P29" t="n">
-        <v>287.1042210254374</v>
+        <v>286.891520328893</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -15993,28 +16123,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1053350672548417</v>
+        <v>0.1269023108574297</v>
       </c>
       <c r="J30" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K30" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L30" t="n">
-        <v>0.003331262037826743</v>
+        <v>0.004879578765958792</v>
       </c>
       <c r="M30" t="n">
-        <v>11.55662680175521</v>
+        <v>11.563436757774</v>
       </c>
       <c r="N30" t="n">
-        <v>212.9208095150366</v>
+        <v>212.5152922764604</v>
       </c>
       <c r="O30" t="n">
-        <v>14.59180624580235</v>
+        <v>14.5779042484323</v>
       </c>
       <c r="P30" t="n">
-        <v>283.0413702951836</v>
+        <v>282.8492645657593</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -16071,28 +16201,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07754843061168271</v>
+        <v>0.09362373425444254</v>
       </c>
       <c r="J31" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K31" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L31" t="n">
-        <v>0.001631450885759</v>
+        <v>0.00241086780489419</v>
       </c>
       <c r="M31" t="n">
-        <v>11.82446688535756</v>
+        <v>11.80742148308111</v>
       </c>
       <c r="N31" t="n">
-        <v>236.0440339852032</v>
+        <v>234.6972766358968</v>
       </c>
       <c r="O31" t="n">
-        <v>15.36372461303584</v>
+        <v>15.3198327874653</v>
       </c>
       <c r="P31" t="n">
-        <v>281.8624920444066</v>
+        <v>281.7193046260738</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16149,28 +16279,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0515053203545527</v>
+        <v>-0.03937538389043579</v>
       </c>
       <c r="J32" t="n">
+        <v>105</v>
+      </c>
+      <c r="K32" t="n">
         <v>104</v>
       </c>
-      <c r="K32" t="n">
-        <v>103</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0006079742728827275</v>
+        <v>0.0003613742319534818</v>
       </c>
       <c r="M32" t="n">
-        <v>13.11044628362825</v>
+        <v>13.06023742604816</v>
       </c>
       <c r="N32" t="n">
-        <v>274.507845027855</v>
+        <v>272.3697148495295</v>
       </c>
       <c r="O32" t="n">
-        <v>16.56827827590589</v>
+        <v>16.50362732400152</v>
       </c>
       <c r="P32" t="n">
-        <v>286.3001413035243</v>
+        <v>286.1900206778069</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -16227,28 +16357,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4063196204502716</v>
+        <v>-0.3861873968420209</v>
       </c>
       <c r="J33" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K33" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03982106508737482</v>
+        <v>0.03657078916096124</v>
       </c>
       <c r="M33" t="n">
-        <v>12.39996795326242</v>
+        <v>12.41196015541816</v>
       </c>
       <c r="N33" t="n">
-        <v>244.447164278253</v>
+        <v>243.4102978834938</v>
       </c>
       <c r="O33" t="n">
-        <v>15.63480617974694</v>
+        <v>15.60161202836085</v>
       </c>
       <c r="P33" t="n">
-        <v>303.5325119977599</v>
+        <v>303.3454986320084</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -16305,28 +16435,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1515103734536694</v>
+        <v>-0.1309076476643389</v>
       </c>
       <c r="J34" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K34" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L34" t="n">
-        <v>0.006047223779479083</v>
+        <v>0.004577835265881958</v>
       </c>
       <c r="M34" t="n">
-        <v>12.51983266768856</v>
+        <v>12.5370874679532</v>
       </c>
       <c r="N34" t="n">
-        <v>238.6567862174474</v>
+        <v>237.7848736808177</v>
       </c>
       <c r="O34" t="n">
-        <v>15.44852051872435</v>
+        <v>15.42027476022453</v>
       </c>
       <c r="P34" t="n">
-        <v>310.9680894086845</v>
+        <v>310.7816563837022</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -16383,28 +16513,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1457034442946467</v>
+        <v>-0.1125249072039818</v>
       </c>
       <c r="J35" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L35" t="n">
-        <v>0.005028381847972274</v>
+        <v>0.003018054317146301</v>
       </c>
       <c r="M35" t="n">
-        <v>13.6017580182417</v>
+        <v>13.69944384982429</v>
       </c>
       <c r="N35" t="n">
-        <v>265.0761973224592</v>
+        <v>266.2051521303816</v>
       </c>
       <c r="O35" t="n">
-        <v>16.28116081004236</v>
+        <v>16.31579456019172</v>
       </c>
       <c r="P35" t="n">
-        <v>318.8665001921091</v>
+        <v>318.5635510062068</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -16461,28 +16591,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1956508782422649</v>
+        <v>-0.1545529059397842</v>
       </c>
       <c r="J36" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K36" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L36" t="n">
-        <v>0.01110155887440223</v>
+        <v>0.006904377974607967</v>
       </c>
       <c r="M36" t="n">
-        <v>12.95619906929464</v>
+        <v>13.12514434890906</v>
       </c>
       <c r="N36" t="n">
-        <v>217.9131978097725</v>
+        <v>221.4653130611912</v>
       </c>
       <c r="O36" t="n">
-        <v>14.76188327449355</v>
+        <v>14.88171069001112</v>
       </c>
       <c r="P36" t="n">
-        <v>335.5726284348081</v>
+        <v>335.2010698252117</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -16539,28 +16669,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1167502964500247</v>
+        <v>-0.07492422468959935</v>
       </c>
       <c r="J37" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K37" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L37" t="n">
-        <v>0.004541526691140718</v>
+        <v>0.001852520437790939</v>
       </c>
       <c r="M37" t="n">
-        <v>11.79718787712932</v>
+        <v>11.94723311240693</v>
       </c>
       <c r="N37" t="n">
-        <v>190.936723314045</v>
+        <v>194.966985583327</v>
       </c>
       <c r="O37" t="n">
-        <v>13.81798550129667</v>
+        <v>13.96305788798883</v>
       </c>
       <c r="P37" t="n">
-        <v>330.209516339283</v>
+        <v>329.8313751270158</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -16598,7 +16728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL105"/>
+  <dimension ref="A1:AL106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35669,6 +35799,198 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>-34.48236470094401,173.00279559655795</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>-34.48302174859073,173.00238134974964</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-34.483714086433245,173.00204964520947</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-34.484401660906755,173.00170681349115</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-34.48516807703418,173.00151285847872</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-34.48591974938653,173.0013980330991</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-34.486663555166935,173.0013579059457</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-34.487403552741014,173.00132680075004</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-34.4881446190284,173.00137734659037</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>-34.48887061228215,173.00151046350572</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-34.48961012491192,173.00153315979946</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>-34.490352648495644,173.00158197099614</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>-34.491090000459565,173.0016731281211</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>-34.49182797690336,173.00175911231037</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>-34.492556510117474,173.00192246451005</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>-34.493302307149634,173.00194422468314</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>-34.494033403619135,173.00208645624187</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>-34.49478221545357,173.00209941850403</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>-34.495521859017614,173.00220143604463</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>-34.496248437326685,173.00238463502882</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>-34.49698219974122,173.00250776124363</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>-34.4977213000394,173.0025930924134</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>-34.49845411739359,173.0027291822618</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>-34.49920889633757,173.00276560946756</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>-34.4999413450415,173.00294773601584</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>-34.500663165851385,173.00314802504133</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>-34.501402262870165,173.00324795906013</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>-34.50214098636722,173.00335002461875</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>-34.502864606644614,173.00353975456161</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>-34.50359286169779,173.00366523619147</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>-34.50427775414924,173.00380668500372</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>-34.504970344563574,173.00400035793146</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>-34.50570009840847,173.00421861893253</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>-34.506429278789746,173.00444699066213</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>-34.50716895743529,173.00472642793255</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>-34.507879970236345,173.00502212988397</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL106"/>
+  <dimension ref="A1:AL107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12677,6 +12677,126 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>305.87</v>
+      </c>
+      <c r="C107" t="n">
+        <v>307.61</v>
+      </c>
+      <c r="D107" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="E107" t="n">
+        <v>314.37</v>
+      </c>
+      <c r="F107" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="G107" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="H107" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="I107" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="J107" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="K107" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="L107" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="M107" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="N107" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="O107" t="n">
+        <v>350.21</v>
+      </c>
+      <c r="P107" t="n">
+        <v>345.73</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>343.96</v>
+      </c>
+      <c r="R107" t="n">
+        <v>341.03</v>
+      </c>
+      <c r="S107" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="T107" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="U107" t="n">
+        <v>329.13</v>
+      </c>
+      <c r="V107" t="n">
+        <v>326.09</v>
+      </c>
+      <c r="W107" t="n">
+        <v>321.07</v>
+      </c>
+      <c r="X107" t="n">
+        <v>317.18</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>310.03</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>312.21</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>301.55</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>293.58</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>293.11</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>292.67</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>292.42</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>289.2</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>296.52</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12688,7 +12808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13771,6 +13891,16 @@
       </c>
       <c r="B108" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -13939,28 +14069,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04618297019732825</v>
+        <v>-0.05017926930144996</v>
       </c>
       <c r="J2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005807814672931233</v>
+        <v>0.0006982939385841158</v>
       </c>
       <c r="M2" t="n">
-        <v>13.44804019717085</v>
+        <v>13.31515359610348</v>
       </c>
       <c r="N2" t="n">
-        <v>249.8548296156929</v>
+        <v>247.0077362807069</v>
       </c>
       <c r="O2" t="n">
-        <v>15.80679694358389</v>
+        <v>15.71647976745133</v>
       </c>
       <c r="P2" t="n">
-        <v>309.3360124671183</v>
+        <v>309.3719611707778</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14017,28 +14147,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04564624307182264</v>
+        <v>0.05482325634943021</v>
       </c>
       <c r="J3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004797798055559133</v>
+        <v>0.0007035340297967263</v>
       </c>
       <c r="M3" t="n">
-        <v>13.49128795502531</v>
+        <v>13.39913503630192</v>
       </c>
       <c r="N3" t="n">
-        <v>289.3322693197931</v>
+        <v>286.3223706247579</v>
       </c>
       <c r="O3" t="n">
-        <v>17.00976981971811</v>
+        <v>16.92106292833751</v>
       </c>
       <c r="P3" t="n">
-        <v>301.105648129486</v>
+        <v>301.0207860295922</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14095,28 +14225,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1165898360809265</v>
+        <v>0.1461508485069074</v>
       </c>
       <c r="J4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00270397489876717</v>
+        <v>0.00427429842751792</v>
       </c>
       <c r="M4" t="n">
-        <v>14.31407139277526</v>
+        <v>14.38575493163244</v>
       </c>
       <c r="N4" t="n">
-        <v>326.1163358295815</v>
+        <v>325.5609473323477</v>
       </c>
       <c r="O4" t="n">
-        <v>18.05869142074202</v>
+        <v>18.04330754968023</v>
       </c>
       <c r="P4" t="n">
-        <v>297.5920415460967</v>
+        <v>297.3114328615778</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14173,28 +14303,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2751777182577507</v>
+        <v>-0.2591824592352958</v>
       </c>
       <c r="J5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01713250147251699</v>
+        <v>0.01545582505421872</v>
       </c>
       <c r="M5" t="n">
-        <v>13.97821186416537</v>
+        <v>13.91999310767707</v>
       </c>
       <c r="N5" t="n">
-        <v>303.0783418755996</v>
+        <v>300.6067042115051</v>
       </c>
       <c r="O5" t="n">
-        <v>17.40914535167076</v>
+        <v>17.33801327175363</v>
       </c>
       <c r="P5" t="n">
-        <v>312.1289854029188</v>
+        <v>311.9886300545518</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14251,28 +14381,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01680347350527462</v>
+        <v>0.001251536750200397</v>
       </c>
       <c r="J6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K6" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L6" t="n">
-        <v>5.166626335317837e-05</v>
+        <v>2.909701951603338e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>14.40318935542138</v>
+        <v>14.36642922806756</v>
       </c>
       <c r="N6" t="n">
-        <v>346.525899998411</v>
+        <v>343.8018318429112</v>
       </c>
       <c r="O6" t="n">
-        <v>18.61520614976936</v>
+        <v>18.54189396590627</v>
       </c>
       <c r="P6" t="n">
-        <v>330.5991891755737</v>
+        <v>330.4270927921866</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14329,28 +14459,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1609177012347066</v>
+        <v>-0.1428789406433991</v>
       </c>
       <c r="J7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003702245529263459</v>
+        <v>0.00296600313378359</v>
       </c>
       <c r="M7" t="n">
-        <v>16.35883675184305</v>
+        <v>16.26335348369361</v>
       </c>
       <c r="N7" t="n">
-        <v>407.6449662258716</v>
+        <v>403.9625251035463</v>
       </c>
       <c r="O7" t="n">
-        <v>20.1902195685404</v>
+        <v>20.09881899773085</v>
       </c>
       <c r="P7" t="n">
-        <v>349.9006634686467</v>
+        <v>349.7148146308879</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14407,28 +14537,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08114159991952113</v>
+        <v>0.09431862651452935</v>
       </c>
       <c r="J8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001130052977578844</v>
+        <v>0.001552548048861957</v>
       </c>
       <c r="M8" t="n">
-        <v>14.65166053167122</v>
+        <v>14.53217498341748</v>
       </c>
       <c r="N8" t="n">
-        <v>338.8852308544656</v>
+        <v>335.390164084321</v>
       </c>
       <c r="O8" t="n">
-        <v>18.40883567351465</v>
+        <v>18.31366058668559</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9876805169342</v>
+        <v>346.8518546922589</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14485,28 +14615,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.00810996308104673</v>
+        <v>0.0009983420253575582</v>
       </c>
       <c r="J9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" t="n">
-        <v>1.000788978555711e-05</v>
+        <v>1.544782839424386e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>15.13253441003714</v>
+        <v>14.9948793790026</v>
       </c>
       <c r="N9" t="n">
-        <v>402.4392673366731</v>
+        <v>398.0791447154295</v>
       </c>
       <c r="O9" t="n">
-        <v>20.06088899666894</v>
+        <v>19.95192082771555</v>
       </c>
       <c r="P9" t="n">
-        <v>353.6892972932565</v>
+        <v>353.6000295802644</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14563,28 +14693,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3429555287676729</v>
+        <v>0.3543352968176277</v>
       </c>
       <c r="J10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K10" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01835561644411599</v>
+        <v>0.01993010520033822</v>
       </c>
       <c r="M10" t="n">
-        <v>16.39686473200792</v>
+        <v>16.25384495535194</v>
       </c>
       <c r="N10" t="n">
-        <v>414.0593610406795</v>
+        <v>409.6772436116405</v>
       </c>
       <c r="O10" t="n">
-        <v>20.34844861508315</v>
+        <v>20.24048526126882</v>
       </c>
       <c r="P10" t="n">
-        <v>356.1757724062599</v>
+        <v>356.0714813735835</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14641,28 +14771,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5271017147644137</v>
+        <v>0.5421551947453119</v>
       </c>
       <c r="J11" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K11" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03562365155173974</v>
+        <v>0.03820701532611115</v>
       </c>
       <c r="M11" t="n">
-        <v>17.26288158509902</v>
+        <v>17.19431023324501</v>
       </c>
       <c r="N11" t="n">
-        <v>496.4236933258694</v>
+        <v>492.0251995773874</v>
       </c>
       <c r="O11" t="n">
-        <v>22.28056761677919</v>
+        <v>22.18164104788885</v>
       </c>
       <c r="P11" t="n">
-        <v>357.5959948578507</v>
+        <v>357.4588098861261</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14719,28 +14849,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3659935804822679</v>
+        <v>0.388539232474463</v>
       </c>
       <c r="J12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02161174987339998</v>
+        <v>0.02460891952243816</v>
       </c>
       <c r="M12" t="n">
-        <v>15.88233953785661</v>
+        <v>15.8925774342454</v>
       </c>
       <c r="N12" t="n">
-        <v>400.2430123359921</v>
+        <v>397.8850273247116</v>
       </c>
       <c r="O12" t="n">
-        <v>20.00607438594569</v>
+        <v>19.94705560539479</v>
       </c>
       <c r="P12" t="n">
-        <v>357.8258913953438</v>
+        <v>357.6204289617414</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -14797,28 +14927,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2349428755232988</v>
+        <v>0.2496298262356032</v>
       </c>
       <c r="J13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009819189118107086</v>
+        <v>0.01125343614328256</v>
       </c>
       <c r="M13" t="n">
-        <v>14.88806522115565</v>
+        <v>14.84878033488646</v>
       </c>
       <c r="N13" t="n">
-        <v>374.622957397246</v>
+        <v>371.5795933422871</v>
       </c>
       <c r="O13" t="n">
-        <v>19.35517908460797</v>
+        <v>19.27639990616212</v>
       </c>
       <c r="P13" t="n">
-        <v>355.8607200903468</v>
+        <v>355.731484391979</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -14875,28 +15005,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1978631358954287</v>
+        <v>0.1978323171664565</v>
       </c>
       <c r="J14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00915135427301117</v>
+        <v>0.0093196751857475</v>
       </c>
       <c r="M14" t="n">
-        <v>12.72028076118065</v>
+        <v>12.59191763357558</v>
       </c>
       <c r="N14" t="n">
-        <v>283.2138167796413</v>
+        <v>280.353074545036</v>
       </c>
       <c r="O14" t="n">
-        <v>16.82895768547896</v>
+        <v>16.74374732683923</v>
       </c>
       <c r="P14" t="n">
-        <v>351.4837474541114</v>
+        <v>351.4840193496578</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -14953,28 +15083,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1629025642815511</v>
+        <v>0.1565870595392591</v>
       </c>
       <c r="J15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>0.008531516925105342</v>
+        <v>0.008030960088219463</v>
       </c>
       <c r="M15" t="n">
-        <v>11.00818057226277</v>
+        <v>10.92409778544554</v>
       </c>
       <c r="N15" t="n">
-        <v>204.3756338382291</v>
+        <v>202.4723350149456</v>
       </c>
       <c r="O15" t="n">
-        <v>14.2960006238888</v>
+        <v>14.22927738906462</v>
       </c>
       <c r="P15" t="n">
-        <v>349.7805565776424</v>
+        <v>349.836460897237</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15031,28 +15161,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1880263081471053</v>
+        <v>0.181851405528318</v>
       </c>
       <c r="J16" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01236590571508989</v>
+        <v>0.01178108884717888</v>
       </c>
       <c r="M16" t="n">
-        <v>10.5209792453898</v>
+        <v>10.44784033296949</v>
       </c>
       <c r="N16" t="n">
-        <v>186.4042073867623</v>
+        <v>184.6947198671653</v>
       </c>
       <c r="O16" t="n">
-        <v>13.65299261652046</v>
+        <v>13.59024355437257</v>
       </c>
       <c r="P16" t="n">
-        <v>344.6013301592504</v>
+        <v>344.6563173007161</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -15109,28 +15239,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1016656341218573</v>
+        <v>0.0991873303651265</v>
       </c>
       <c r="J17" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003318482497371211</v>
+        <v>0.003218097547300514</v>
       </c>
       <c r="M17" t="n">
-        <v>11.11157510263244</v>
+        <v>11.01783342191731</v>
       </c>
       <c r="N17" t="n">
-        <v>196.9497790838796</v>
+        <v>195.0769208944733</v>
       </c>
       <c r="O17" t="n">
-        <v>14.03387968752332</v>
+        <v>13.96699398204472</v>
       </c>
       <c r="P17" t="n">
-        <v>342.8106871750954</v>
+        <v>342.8333377656551</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -15187,28 +15317,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.009397708278787029</v>
+        <v>-0.002953455099866862</v>
       </c>
       <c r="J18" t="n">
+        <v>106</v>
+      </c>
+      <c r="K18" t="n">
         <v>105</v>
       </c>
-      <c r="K18" t="n">
-        <v>104</v>
-      </c>
       <c r="L18" t="n">
-        <v>2.564304108187976e-05</v>
+        <v>2.577429261907405e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>11.9792913791505</v>
+        <v>11.89916353356602</v>
       </c>
       <c r="N18" t="n">
-        <v>224.8446516064881</v>
+        <v>222.8525946863779</v>
       </c>
       <c r="O18" t="n">
-        <v>14.99482082608819</v>
+        <v>14.92824821224439</v>
       </c>
       <c r="P18" t="n">
-        <v>337.2625673972888</v>
+        <v>337.2049202532467</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15265,28 +15395,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1083689146267544</v>
+        <v>0.102990932813725</v>
       </c>
       <c r="J19" t="n">
+        <v>106</v>
+      </c>
+      <c r="K19" t="n">
         <v>105</v>
       </c>
-      <c r="K19" t="n">
-        <v>104</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.003288736673437986</v>
+        <v>0.00302483510017082</v>
       </c>
       <c r="M19" t="n">
-        <v>11.7492597301354</v>
+        <v>11.66924233921036</v>
       </c>
       <c r="N19" t="n">
-        <v>225.0026874556807</v>
+        <v>222.9594801257955</v>
       </c>
       <c r="O19" t="n">
-        <v>15.00008958158853</v>
+        <v>14.93182775569674</v>
       </c>
       <c r="P19" t="n">
-        <v>332.228825750396</v>
+        <v>332.2782475751571</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15343,28 +15473,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1417005627394742</v>
+        <v>0.1377800490596439</v>
       </c>
       <c r="J20" t="n">
+        <v>106</v>
+      </c>
+      <c r="K20" t="n">
         <v>105</v>
       </c>
-      <c r="K20" t="n">
-        <v>104</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.004904220469117315</v>
+        <v>0.004722283151422313</v>
       </c>
       <c r="M20" t="n">
-        <v>13.36246092380628</v>
+        <v>13.25840087613277</v>
       </c>
       <c r="N20" t="n">
-        <v>257.5585917421552</v>
+        <v>255.1586234241159</v>
       </c>
       <c r="O20" t="n">
-        <v>16.04863208320744</v>
+        <v>15.97368534259129</v>
       </c>
       <c r="P20" t="n">
-        <v>325.3672581564446</v>
+        <v>325.4032863444888</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -15421,28 +15551,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.292144710199417</v>
+        <v>0.2996139481456203</v>
       </c>
       <c r="J21" t="n">
+        <v>106</v>
+      </c>
+      <c r="K21" t="n">
         <v>105</v>
       </c>
-      <c r="K21" t="n">
-        <v>104</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02055764269448446</v>
+        <v>0.02197395945023961</v>
       </c>
       <c r="M21" t="n">
-        <v>13.35123375136314</v>
+        <v>13.26634382274581</v>
       </c>
       <c r="N21" t="n">
-        <v>257.0630260560208</v>
+        <v>254.8070725217907</v>
       </c>
       <c r="O21" t="n">
-        <v>16.03318515005739</v>
+        <v>15.96267748599184</v>
       </c>
       <c r="P21" t="n">
-        <v>316.9881436575157</v>
+        <v>316.919503899757</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -15499,28 +15629,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.291168598719825</v>
+        <v>0.3030793226261775</v>
       </c>
       <c r="J22" t="n">
+        <v>106</v>
+      </c>
+      <c r="K22" t="n">
         <v>105</v>
       </c>
-      <c r="K22" t="n">
-        <v>104</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.02294876425759651</v>
+        <v>0.02521161658620019</v>
       </c>
       <c r="M22" t="n">
-        <v>12.4953837516514</v>
+        <v>12.44068057858399</v>
       </c>
       <c r="N22" t="n">
-        <v>228.1839531107526</v>
+        <v>226.4996789550341</v>
       </c>
       <c r="O22" t="n">
-        <v>15.10575893858871</v>
+        <v>15.04990627728406</v>
       </c>
       <c r="P22" t="n">
-        <v>311.2608655556371</v>
+        <v>311.1514100516686</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -15577,28 +15707,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.113119553696978</v>
+        <v>0.1296677662599144</v>
       </c>
       <c r="J23" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K23" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003750592164399325</v>
+        <v>0.004992079647581638</v>
       </c>
       <c r="M23" t="n">
-        <v>11.6927138458107</v>
+        <v>11.68459465053963</v>
       </c>
       <c r="N23" t="n">
-        <v>218.5299715937845</v>
+        <v>217.3795579893355</v>
       </c>
       <c r="O23" t="n">
-        <v>14.78275926861371</v>
+        <v>14.74379727171177</v>
       </c>
       <c r="P23" t="n">
-        <v>308.0496061987427</v>
+        <v>307.8998830615609</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -15655,28 +15785,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1620603071842592</v>
+        <v>0.1806228891578321</v>
       </c>
       <c r="J24" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K24" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L24" t="n">
-        <v>0.005737595396035911</v>
+        <v>0.007221941915356189</v>
       </c>
       <c r="M24" t="n">
-        <v>13.65206844209169</v>
+        <v>13.63390246856858</v>
       </c>
       <c r="N24" t="n">
-        <v>279.6502904373605</v>
+        <v>278.0367839129486</v>
       </c>
       <c r="O24" t="n">
-        <v>16.72274769400533</v>
+        <v>16.67443504029293</v>
       </c>
       <c r="P24" t="n">
-        <v>302.0851229205801</v>
+        <v>301.9098451047435</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -15733,28 +15863,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.115850535626856</v>
+        <v>0.1321721977133329</v>
       </c>
       <c r="J25" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K25" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003027702986857395</v>
+        <v>0.003998599799748592</v>
       </c>
       <c r="M25" t="n">
-        <v>13.51644353295141</v>
+        <v>13.47928243751033</v>
       </c>
       <c r="N25" t="n">
-        <v>274.8218933730634</v>
+        <v>273.0370937386039</v>
       </c>
       <c r="O25" t="n">
-        <v>16.57775296513564</v>
+        <v>16.52383411132549</v>
       </c>
       <c r="P25" t="n">
-        <v>297.3449355348445</v>
+        <v>297.1928312188676</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -15811,28 +15941,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5114475795754879</v>
+        <v>0.5388488534039256</v>
       </c>
       <c r="J26" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03417271142528</v>
+        <v>0.0382834035880224</v>
       </c>
       <c r="M26" t="n">
-        <v>17.78640871346768</v>
+        <v>17.7787175488992</v>
       </c>
       <c r="N26" t="n">
-        <v>458.1259176046777</v>
+        <v>456.0520959260933</v>
       </c>
       <c r="O26" t="n">
-        <v>21.4038762284937</v>
+        <v>21.35537627685575</v>
       </c>
       <c r="P26" t="n">
-        <v>282.9259701662417</v>
+        <v>282.6689429307548</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -15889,28 +16019,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2709881193678548</v>
+        <v>0.2892208426876338</v>
       </c>
       <c r="J27" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01169829176073034</v>
+        <v>0.01351178390814212</v>
       </c>
       <c r="M27" t="n">
-        <v>15.71725298786471</v>
+        <v>15.64535495348267</v>
       </c>
       <c r="N27" t="n">
-        <v>392.9153121019764</v>
+        <v>390.1547655490382</v>
       </c>
       <c r="O27" t="n">
-        <v>19.8220915168399</v>
+        <v>19.7523356985709</v>
       </c>
       <c r="P27" t="n">
-        <v>283.6784726055903</v>
+        <v>283.5100869294524</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -15967,28 +16097,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1801862236772125</v>
+        <v>-0.1669552826452066</v>
       </c>
       <c r="J28" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K28" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L28" t="n">
-        <v>0.007611020220840148</v>
+        <v>0.006650399291310061</v>
       </c>
       <c r="M28" t="n">
-        <v>12.96679193607639</v>
+        <v>12.89373424391609</v>
       </c>
       <c r="N28" t="n">
-        <v>257.7579559420625</v>
+        <v>255.7960192166043</v>
       </c>
       <c r="O28" t="n">
-        <v>16.05484213382562</v>
+        <v>15.99362433023248</v>
       </c>
       <c r="P28" t="n">
-        <v>290.5587654021401</v>
+        <v>290.4330148109914</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -16045,28 +16175,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1066857554180887</v>
+        <v>-0.09224447873072948</v>
       </c>
       <c r="J29" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K29" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002927805215094281</v>
+        <v>0.002223968363098128</v>
       </c>
       <c r="M29" t="n">
-        <v>13.06750055254265</v>
+        <v>13.02419911759661</v>
       </c>
       <c r="N29" t="n">
-        <v>250.8159312237903</v>
+        <v>249.1908017744229</v>
       </c>
       <c r="O29" t="n">
-        <v>15.83716929327303</v>
+        <v>15.78577846589844</v>
       </c>
       <c r="P29" t="n">
-        <v>286.891520328893</v>
+        <v>286.7617348361308</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -16123,28 +16253,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1269023108574297</v>
+        <v>0.1373920898554293</v>
       </c>
       <c r="J30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L30" t="n">
-        <v>0.004879578765958792</v>
+        <v>0.005808457088726127</v>
       </c>
       <c r="M30" t="n">
-        <v>11.563436757774</v>
+        <v>11.5102165008362</v>
       </c>
       <c r="N30" t="n">
-        <v>212.5152922764604</v>
+        <v>210.9014285816735</v>
       </c>
       <c r="O30" t="n">
-        <v>14.5779042484323</v>
+        <v>14.52244568182899</v>
       </c>
       <c r="P30" t="n">
-        <v>282.8492645657593</v>
+        <v>282.7549916586129</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -16201,28 +16331,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09362373425444254</v>
+        <v>0.1069060930248857</v>
       </c>
       <c r="J31" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K31" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00241086780489419</v>
+        <v>0.00319009093780942</v>
       </c>
       <c r="M31" t="n">
-        <v>11.80742148308111</v>
+        <v>11.77296974478529</v>
       </c>
       <c r="N31" t="n">
-        <v>234.6972766358968</v>
+        <v>233.1100420113268</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3198327874653</v>
+        <v>15.2679416429107</v>
       </c>
       <c r="P31" t="n">
-        <v>281.7193046260738</v>
+        <v>281.5999344682002</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16279,28 +16409,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.03937538389043579</v>
+        <v>-0.03279346815052001</v>
       </c>
       <c r="J32" t="n">
+        <v>106</v>
+      </c>
+      <c r="K32" t="n">
         <v>105</v>
       </c>
-      <c r="K32" t="n">
-        <v>104</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0003613742319534818</v>
+        <v>0.0002551690408447715</v>
       </c>
       <c r="M32" t="n">
-        <v>13.06023742604816</v>
+        <v>12.97601792605002</v>
       </c>
       <c r="N32" t="n">
-        <v>272.3697148495295</v>
+        <v>269.9261055812601</v>
       </c>
       <c r="O32" t="n">
-        <v>16.50362732400152</v>
+        <v>16.42942803573089</v>
       </c>
       <c r="P32" t="n">
-        <v>286.1900206778069</v>
+        <v>286.1297392136833</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -16357,28 +16487,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3861873968420209</v>
+        <v>-0.3808327250692826</v>
       </c>
       <c r="J33" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K33" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03657078916096124</v>
+        <v>0.03622391561353089</v>
       </c>
       <c r="M33" t="n">
-        <v>12.41196015541816</v>
+        <v>12.3270388192873</v>
       </c>
       <c r="N33" t="n">
-        <v>243.4102978834938</v>
+        <v>241.1661303525754</v>
       </c>
       <c r="O33" t="n">
-        <v>15.60161202836085</v>
+        <v>15.52952447284125</v>
       </c>
       <c r="P33" t="n">
-        <v>303.3454986320084</v>
+        <v>303.295327402046</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -16435,28 +16565,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1309076476643389</v>
+        <v>-0.1227234480073351</v>
       </c>
       <c r="J34" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K34" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L34" t="n">
-        <v>0.004577835265881958</v>
+        <v>0.004095916010735445</v>
       </c>
       <c r="M34" t="n">
-        <v>12.5370874679532</v>
+        <v>12.47174169909026</v>
       </c>
       <c r="N34" t="n">
-        <v>237.7848736808177</v>
+        <v>235.7308693302447</v>
       </c>
       <c r="O34" t="n">
-        <v>15.42027476022453</v>
+        <v>15.35352953982389</v>
       </c>
       <c r="P34" t="n">
-        <v>310.7816563837022</v>
+        <v>310.7069385716545</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -16513,28 +16643,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1125249072039818</v>
+        <v>-0.09474031217076065</v>
       </c>
       <c r="J35" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K35" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" t="n">
-        <v>0.003018054317146301</v>
+        <v>0.002171766293556421</v>
       </c>
       <c r="M35" t="n">
-        <v>13.69944384982429</v>
+        <v>13.68921023385251</v>
       </c>
       <c r="N35" t="n">
-        <v>266.2051521303816</v>
+        <v>264.6939647669307</v>
       </c>
       <c r="O35" t="n">
-        <v>16.31579456019172</v>
+        <v>16.26941808322998</v>
       </c>
       <c r="P35" t="n">
-        <v>318.5635510062068</v>
+        <v>318.3996947605872</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -16591,28 +16721,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1545529059397842</v>
+        <v>-0.1376286861689236</v>
       </c>
       <c r="J36" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K36" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>0.006904377974607967</v>
+        <v>0.005559870591247407</v>
       </c>
       <c r="M36" t="n">
-        <v>13.12514434890906</v>
+        <v>13.11454858992312</v>
       </c>
       <c r="N36" t="n">
-        <v>221.4653130611912</v>
+        <v>220.2453493990796</v>
       </c>
       <c r="O36" t="n">
-        <v>14.88171069001112</v>
+        <v>14.84066539610268</v>
       </c>
       <c r="P36" t="n">
-        <v>335.2010698252117</v>
+        <v>335.0466555701669</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -16669,28 +16799,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.07492422468959935</v>
+        <v>-0.02095847003565362</v>
       </c>
       <c r="J37" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K37" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>0.001852520437790939</v>
+        <v>0.0001405584279946526</v>
       </c>
       <c r="M37" t="n">
-        <v>11.94723311240693</v>
+        <v>12.17057088916294</v>
       </c>
       <c r="N37" t="n">
-        <v>194.966985583327</v>
+        <v>203.1309376978252</v>
       </c>
       <c r="O37" t="n">
-        <v>13.96305788798883</v>
+        <v>14.2524011204367</v>
       </c>
       <c r="P37" t="n">
-        <v>329.8313751270158</v>
+        <v>329.3389989988609</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -16728,7 +16858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL106"/>
+  <dimension ref="A1:AL107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35991,6 +36121,198 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-34.48236461818888,173.00279540302645</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>-34.48302952761015,173.0023995418302</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>-34.48372836180873,173.0020830298592</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-34.484372903132844,173.00163955990683</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-34.48515290338523,173.0014697614778</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-34.485909740902194,173.0013313779296</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-34.48666189669594,173.00130272426966</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-34.48740264336078,173.00129654307457</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-34.488144571776296,173.00140457482942</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-34.48886844720128,173.00153833203942</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-34.4895929336666,173.00167409966312</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>-34.49033851961608,173.00169780563007</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>-34.4910896850244,173.00167571421963</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>-34.49183056610495,173.0017378845648</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>-34.49256891731883,173.00182074286036</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>-34.49330370033294,173.00193280244815</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>-34.49404000155734,173.00203236179317</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>-34.4947867512501,173.00206400445066</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>-34.49552841804124,173.00215383800682</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>-34.4962558614976,173.0023321315629</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>-34.49699023123688,173.0024509625244</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>-34.49772760075339,173.00254853348196</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>-34.498464263347834,173.00265845344595</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>-34.49921305881835,173.00273940008384</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>-34.4999413450415,173.00294773601584</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>-34.50068568258902,173.00301727629466</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>-34.50142507349913,173.00311550280793</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>-34.50215068367328,173.0032937142309</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>-34.5028762324571,173.0034722455178</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>-34.503595154003214,173.00365123714585</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>-34.50428126954153,173.00377329326344</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>-34.50497547423888,173.00390884413312</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>-34.5057043996655,173.00414188580237</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>-34.506434439229395,173.00435493185353</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>-34.50719491290164,173.0045835233954</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>-34.50785325950554,173.00510659597708</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL107"/>
+  <dimension ref="A1:AL108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12789,11 +12789,131 @@
         <v>341.3</v>
       </c>
       <c r="AK107" t="n">
-        <v>360.14</v>
+        <v>348.53</v>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>305.87</v>
+      </c>
+      <c r="C108" t="n">
+        <v>307.61</v>
+      </c>
+      <c r="D108" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="E108" t="n">
+        <v>314.37</v>
+      </c>
+      <c r="F108" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="G108" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="H108" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="I108" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="J108" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="K108" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="L108" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="M108" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="N108" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="O108" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="P108" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>338.52</v>
+      </c>
+      <c r="R108" t="n">
+        <v>335.01</v>
+      </c>
+      <c r="S108" t="n">
+        <v>327.74</v>
+      </c>
+      <c r="T108" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="U108" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="V108" t="n">
+        <v>319.73</v>
+      </c>
+      <c r="W108" t="n">
+        <v>313.83</v>
+      </c>
+      <c r="X108" t="n">
+        <v>308.76</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>303.96</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>297.57</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>292.36</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>285.25</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>286.34</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>286.59</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>281.38</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>290.06</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>305.12</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>319.41</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>340.31</v>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13901,6 +14021,16 @@
       </c>
       <c r="B109" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -14069,28 +14199,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05017926930144996</v>
+        <v>-0.05394948096333388</v>
       </c>
       <c r="J2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006982939385841158</v>
+        <v>0.0008215078282548527</v>
       </c>
       <c r="M2" t="n">
-        <v>13.31515359610348</v>
+        <v>13.18395773872977</v>
       </c>
       <c r="N2" t="n">
-        <v>247.0077362807069</v>
+        <v>244.222697478376</v>
       </c>
       <c r="O2" t="n">
-        <v>15.71647976745133</v>
+        <v>15.62762609862343</v>
       </c>
       <c r="P2" t="n">
-        <v>309.3719611707778</v>
+        <v>309.4059286092581</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14147,28 +14277,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05482325634943021</v>
+        <v>0.06350151588516394</v>
       </c>
       <c r="J3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007035340297967263</v>
+        <v>0.0009589331703073745</v>
       </c>
       <c r="M3" t="n">
-        <v>13.39913503630192</v>
+        <v>13.30585983057914</v>
       </c>
       <c r="N3" t="n">
-        <v>286.3223706247579</v>
+        <v>283.3632034698821</v>
       </c>
       <c r="O3" t="n">
-        <v>16.92106292833751</v>
+        <v>16.83339548248903</v>
       </c>
       <c r="P3" t="n">
-        <v>301.0207860295922</v>
+        <v>300.9404105329363</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14225,28 +14355,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1461508485069074</v>
+        <v>0.1741124059708366</v>
       </c>
       <c r="J4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00427429842751792</v>
+        <v>0.006101049389206192</v>
       </c>
       <c r="M4" t="n">
-        <v>14.38575493163244</v>
+        <v>14.44268306521101</v>
       </c>
       <c r="N4" t="n">
-        <v>325.5609473323477</v>
+        <v>324.8378940630272</v>
       </c>
       <c r="O4" t="n">
-        <v>18.04330754968023</v>
+        <v>18.02325980678932</v>
       </c>
       <c r="P4" t="n">
-        <v>297.3114328615778</v>
+        <v>297.045592870417</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14303,28 +14433,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2591824592352958</v>
+        <v>-0.2440582948858199</v>
       </c>
       <c r="J5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01545582505421872</v>
+        <v>0.0139278897468349</v>
       </c>
       <c r="M5" t="n">
-        <v>13.91999310767707</v>
+        <v>13.8574572137703</v>
       </c>
       <c r="N5" t="n">
-        <v>300.6067042115051</v>
+        <v>298.1369238867372</v>
       </c>
       <c r="O5" t="n">
-        <v>17.33801327175363</v>
+        <v>17.26664194007443</v>
       </c>
       <c r="P5" t="n">
-        <v>311.9886300545518</v>
+        <v>311.8557090151783</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14381,28 +14511,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001251536750200397</v>
+        <v>0.01832222938731723</v>
       </c>
       <c r="J6" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K6" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L6" t="n">
-        <v>2.909701951603338e-07</v>
+        <v>6.327394414484822e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>14.36642922806756</v>
+        <v>14.32359668410281</v>
       </c>
       <c r="N6" t="n">
-        <v>343.8018318429112</v>
+        <v>341.0746401787357</v>
       </c>
       <c r="O6" t="n">
-        <v>18.54189396590627</v>
+        <v>18.46820619818654</v>
       </c>
       <c r="P6" t="n">
-        <v>330.4270927921866</v>
+        <v>330.2641477467698</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14459,28 +14589,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1428789406433991</v>
+        <v>-0.125820278196255</v>
       </c>
       <c r="J7" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00296600313378359</v>
+        <v>0.002335913774387577</v>
       </c>
       <c r="M7" t="n">
-        <v>16.26335348369361</v>
+        <v>16.16745448607763</v>
       </c>
       <c r="N7" t="n">
-        <v>403.9625251035463</v>
+        <v>400.3059735120056</v>
       </c>
       <c r="O7" t="n">
-        <v>20.09881899773085</v>
+        <v>20.00764787555013</v>
       </c>
       <c r="P7" t="n">
-        <v>349.7148146308879</v>
+        <v>349.5388169731774</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14537,28 +14667,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09431862651452935</v>
+        <v>0.1067465673919814</v>
       </c>
       <c r="J8" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001552548048861957</v>
+        <v>0.002020782408766131</v>
       </c>
       <c r="M8" t="n">
-        <v>14.53217498341748</v>
+        <v>14.41226067396791</v>
       </c>
       <c r="N8" t="n">
-        <v>335.390164084321</v>
+        <v>331.9457246730945</v>
       </c>
       <c r="O8" t="n">
-        <v>18.31366058668559</v>
+        <v>18.21937772463962</v>
       </c>
       <c r="P8" t="n">
-        <v>346.8518546922589</v>
+        <v>346.7235736519334</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14615,28 +14745,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009983420253575582</v>
+        <v>0.009590946880988519</v>
       </c>
       <c r="J9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.544782839424386e-07</v>
+        <v>1.451237135208228e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>14.9948793790026</v>
+        <v>14.8582248458631</v>
       </c>
       <c r="N9" t="n">
-        <v>398.0791447154295</v>
+        <v>393.8027061605298</v>
       </c>
       <c r="O9" t="n">
-        <v>19.95192082771555</v>
+        <v>19.84446285895715</v>
       </c>
       <c r="P9" t="n">
-        <v>353.6000295802644</v>
+        <v>353.5157005914318</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14693,28 +14823,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3543352968176277</v>
+        <v>0.3650409461329495</v>
       </c>
       <c r="J10" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01993010520033822</v>
+        <v>0.02150102488298866</v>
       </c>
       <c r="M10" t="n">
-        <v>16.25384495535194</v>
+        <v>16.11119327660629</v>
       </c>
       <c r="N10" t="n">
-        <v>409.6772436116405</v>
+        <v>405.3691792806471</v>
       </c>
       <c r="O10" t="n">
-        <v>20.24048526126882</v>
+        <v>20.1337820411528</v>
       </c>
       <c r="P10" t="n">
-        <v>356.0714813735835</v>
+        <v>355.9732270477673</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14771,28 +14901,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5421551947453119</v>
+        <v>0.5563910940982814</v>
       </c>
       <c r="J11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K11" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03820701532611115</v>
+        <v>0.04077395114659599</v>
       </c>
       <c r="M11" t="n">
-        <v>17.19431023324501</v>
+        <v>17.12087834870599</v>
       </c>
       <c r="N11" t="n">
-        <v>492.0251995773874</v>
+        <v>487.6712429996705</v>
       </c>
       <c r="O11" t="n">
-        <v>22.18164104788885</v>
+        <v>22.08327971565072</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4588098861261</v>
+        <v>357.3288906818055</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14849,28 +14979,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.388539232474463</v>
+        <v>0.4098755222376244</v>
       </c>
       <c r="J12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02460891952243816</v>
+        <v>0.02765887111849363</v>
       </c>
       <c r="M12" t="n">
-        <v>15.8925774342454</v>
+        <v>15.89897933754574</v>
       </c>
       <c r="N12" t="n">
-        <v>397.8850273247116</v>
+        <v>395.4729770108664</v>
       </c>
       <c r="O12" t="n">
-        <v>19.94705560539479</v>
+        <v>19.88650238254245</v>
       </c>
       <c r="P12" t="n">
-        <v>357.6204289617414</v>
+        <v>357.4257104040685</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -14927,28 +15057,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2496298262356032</v>
+        <v>0.2635218624177769</v>
       </c>
       <c r="J13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01125343614328256</v>
+        <v>0.01272410343602948</v>
       </c>
       <c r="M13" t="n">
-        <v>14.84878033488646</v>
+        <v>14.80406924189759</v>
       </c>
       <c r="N13" t="n">
-        <v>371.5795933422871</v>
+        <v>368.5540476654145</v>
       </c>
       <c r="O13" t="n">
-        <v>19.27639990616212</v>
+        <v>19.19776152746498</v>
       </c>
       <c r="P13" t="n">
-        <v>355.731484391979</v>
+        <v>355.6090736410777</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15005,28 +15135,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1978323171664565</v>
+        <v>0.1879387651754064</v>
       </c>
       <c r="J14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0093196751857475</v>
+        <v>0.008559529025328416</v>
       </c>
       <c r="M14" t="n">
-        <v>12.59191763357558</v>
+        <v>12.5085199289039</v>
       </c>
       <c r="N14" t="n">
-        <v>280.353074545036</v>
+        <v>277.9141848018668</v>
       </c>
       <c r="O14" t="n">
-        <v>16.74374732683923</v>
+        <v>16.67075837512699</v>
       </c>
       <c r="P14" t="n">
-        <v>351.4840193496578</v>
+        <v>351.5714234208596</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15083,28 +15213,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1565870595392591</v>
+        <v>0.1430743008724709</v>
       </c>
       <c r="J15" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L15" t="n">
-        <v>0.008030960088219463</v>
+        <v>0.006813183144480428</v>
       </c>
       <c r="M15" t="n">
-        <v>10.92409778544554</v>
+        <v>10.8708823680572</v>
       </c>
       <c r="N15" t="n">
-        <v>202.4723350149456</v>
+        <v>201.1389756354937</v>
       </c>
       <c r="O15" t="n">
-        <v>14.22927738906462</v>
+        <v>14.18234732459665</v>
       </c>
       <c r="P15" t="n">
-        <v>349.836460897237</v>
+        <v>349.9562348560098</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15161,28 +15291,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.181851405528318</v>
+        <v>0.1628761859563641</v>
       </c>
       <c r="J16" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K16" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01178108884717888</v>
+        <v>0.009572439329947446</v>
       </c>
       <c r="M16" t="n">
-        <v>10.44784033296949</v>
+        <v>10.44581172620155</v>
       </c>
       <c r="N16" t="n">
-        <v>184.6947198671653</v>
+        <v>184.2247503486551</v>
       </c>
       <c r="O16" t="n">
-        <v>13.59024355437257</v>
+        <v>13.57294184577003</v>
       </c>
       <c r="P16" t="n">
-        <v>344.6563173007161</v>
+        <v>344.8255170179992</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -15239,28 +15369,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0991873303651265</v>
+        <v>0.08805890833364226</v>
       </c>
       <c r="J17" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K17" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003218097547300514</v>
+        <v>0.002578434999412682</v>
       </c>
       <c r="M17" t="n">
-        <v>11.01783342191731</v>
+        <v>10.97105215964925</v>
       </c>
       <c r="N17" t="n">
-        <v>195.0769208944733</v>
+        <v>193.6584790904788</v>
       </c>
       <c r="O17" t="n">
-        <v>13.96699398204472</v>
+        <v>13.91612299063496</v>
       </c>
       <c r="P17" t="n">
-        <v>342.8333377656551</v>
+        <v>342.9351744168424</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -15317,28 +15447,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.002953455099866862</v>
+        <v>-0.006265175031269333</v>
       </c>
       <c r="J18" t="n">
+        <v>107</v>
+      </c>
+      <c r="K18" t="n">
         <v>106</v>
       </c>
-      <c r="K18" t="n">
-        <v>105</v>
-      </c>
       <c r="L18" t="n">
-        <v>2.577429261907405e-06</v>
+        <v>1.18013998956501e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>11.89916353356602</v>
+        <v>11.8085124079758</v>
       </c>
       <c r="N18" t="n">
-        <v>222.8525946863779</v>
+        <v>220.7913108713012</v>
       </c>
       <c r="O18" t="n">
-        <v>14.92824821224439</v>
+        <v>14.85904811457656</v>
       </c>
       <c r="P18" t="n">
-        <v>337.2049202532467</v>
+        <v>337.234583989311</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15395,28 +15525,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.102990932813725</v>
+        <v>0.09145227504300686</v>
       </c>
       <c r="J19" t="n">
+        <v>107</v>
+      </c>
+      <c r="K19" t="n">
         <v>106</v>
       </c>
-      <c r="K19" t="n">
-        <v>105</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.00302483510017082</v>
+        <v>0.002423923088222257</v>
       </c>
       <c r="M19" t="n">
-        <v>11.66924233921036</v>
+        <v>11.6288928917828</v>
       </c>
       <c r="N19" t="n">
-        <v>222.9594801257955</v>
+        <v>221.334445565265</v>
       </c>
       <c r="O19" t="n">
-        <v>14.93182775569674</v>
+        <v>14.87731311646243</v>
       </c>
       <c r="P19" t="n">
-        <v>332.2782475751571</v>
+        <v>332.384417400023</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15473,28 +15603,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1377800490596439</v>
+        <v>0.1290036082514321</v>
       </c>
       <c r="J20" t="n">
+        <v>107</v>
+      </c>
+      <c r="K20" t="n">
         <v>106</v>
       </c>
-      <c r="K20" t="n">
-        <v>105</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.004722283151422313</v>
+        <v>0.00421147935358035</v>
       </c>
       <c r="M20" t="n">
-        <v>13.25840087613277</v>
+        <v>13.18682677287711</v>
       </c>
       <c r="N20" t="n">
-        <v>255.1586234241159</v>
+        <v>253.0282105828275</v>
       </c>
       <c r="O20" t="n">
-        <v>15.97368534259129</v>
+        <v>15.90686048794128</v>
       </c>
       <c r="P20" t="n">
-        <v>325.4032863444888</v>
+        <v>325.4840403803628</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -15551,28 +15681,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2996139481456203</v>
+        <v>0.2987962187178296</v>
       </c>
       <c r="J21" t="n">
+        <v>107</v>
+      </c>
+      <c r="K21" t="n">
         <v>106</v>
       </c>
-      <c r="K21" t="n">
-        <v>105</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02197395945023961</v>
+        <v>0.02223906976025969</v>
       </c>
       <c r="M21" t="n">
-        <v>13.26634382274581</v>
+        <v>13.14600846891402</v>
       </c>
       <c r="N21" t="n">
-        <v>254.8070725217907</v>
+        <v>252.4056346994337</v>
       </c>
       <c r="O21" t="n">
-        <v>15.96267748599184</v>
+        <v>15.88727902126206</v>
       </c>
       <c r="P21" t="n">
-        <v>316.919503899757</v>
+        <v>316.9270280149411</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -15629,28 +15759,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3030793226261775</v>
+        <v>0.3041885984799714</v>
       </c>
       <c r="J22" t="n">
+        <v>107</v>
+      </c>
+      <c r="K22" t="n">
         <v>106</v>
       </c>
-      <c r="K22" t="n">
-        <v>105</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.02521161658620019</v>
+        <v>0.02583402222243392</v>
       </c>
       <c r="M22" t="n">
-        <v>12.44068057858399</v>
+        <v>12.32946385594571</v>
       </c>
       <c r="N22" t="n">
-        <v>226.4996789550341</v>
+        <v>224.3673105302775</v>
       </c>
       <c r="O22" t="n">
-        <v>15.04990627728406</v>
+        <v>14.97889550435136</v>
       </c>
       <c r="P22" t="n">
-        <v>311.1514100516686</v>
+        <v>311.1412033512477</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -15707,28 +15837,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1296677662599144</v>
+        <v>0.1337568651847172</v>
       </c>
       <c r="J23" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K23" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004992079647581638</v>
+        <v>0.005404073692697242</v>
       </c>
       <c r="M23" t="n">
-        <v>11.68459465053963</v>
+        <v>11.59915492676645</v>
       </c>
       <c r="N23" t="n">
-        <v>217.3795579893355</v>
+        <v>215.3698314511603</v>
       </c>
       <c r="O23" t="n">
-        <v>14.74379727171177</v>
+        <v>14.67548402783228</v>
       </c>
       <c r="P23" t="n">
-        <v>307.8998830615609</v>
+        <v>307.8628388301797</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -15785,28 +15915,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1806228891578321</v>
+        <v>0.1842121396057775</v>
       </c>
       <c r="J24" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K24" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L24" t="n">
-        <v>0.007221941915356189</v>
+        <v>0.007644773826501083</v>
       </c>
       <c r="M24" t="n">
-        <v>13.63390246856858</v>
+        <v>13.52364251890126</v>
       </c>
       <c r="N24" t="n">
-        <v>278.0367839129486</v>
+        <v>275.3814166575919</v>
       </c>
       <c r="O24" t="n">
-        <v>16.67443504029293</v>
+        <v>16.59462011187939</v>
       </c>
       <c r="P24" t="n">
-        <v>301.9098451047435</v>
+        <v>301.8759116837339</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -15863,28 +15993,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1321721977133329</v>
+        <v>0.1376479996141705</v>
       </c>
       <c r="J25" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K25" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003998599799748592</v>
+        <v>0.004412559566954521</v>
       </c>
       <c r="M25" t="n">
-        <v>13.47928243751033</v>
+        <v>13.38198426936529</v>
       </c>
       <c r="N25" t="n">
-        <v>273.0370937386039</v>
+        <v>270.515493823352</v>
       </c>
       <c r="O25" t="n">
-        <v>16.52383411132549</v>
+        <v>16.44735522275092</v>
       </c>
       <c r="P25" t="n">
-        <v>297.1928312188676</v>
+        <v>297.1417381101057</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -15941,28 +16071,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5388488534039256</v>
+        <v>0.5403368487190764</v>
       </c>
       <c r="J26" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K26" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0382834035880224</v>
+        <v>0.03916743079005869</v>
       </c>
       <c r="M26" t="n">
-        <v>17.7787175488992</v>
+        <v>17.61345374736327</v>
       </c>
       <c r="N26" t="n">
-        <v>456.0520959260933</v>
+        <v>451.5885767241456</v>
       </c>
       <c r="O26" t="n">
-        <v>21.35537627685575</v>
+        <v>21.25061356112208</v>
       </c>
       <c r="P26" t="n">
-        <v>282.6689429307548</v>
+        <v>282.6549679725146</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -16019,28 +16149,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2892208426876338</v>
+        <v>0.2913985649210444</v>
       </c>
       <c r="J27" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K27" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01351178390814212</v>
+        <v>0.01395822995634755</v>
       </c>
       <c r="M27" t="n">
-        <v>15.64535495348267</v>
+        <v>15.50184817510471</v>
       </c>
       <c r="N27" t="n">
-        <v>390.1547655490382</v>
+        <v>386.3465356352244</v>
       </c>
       <c r="O27" t="n">
-        <v>19.7523356985709</v>
+        <v>19.65569982562881</v>
       </c>
       <c r="P27" t="n">
-        <v>283.5100869294524</v>
+        <v>283.4899490935372</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -16097,28 +16227,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1669552826452066</v>
+        <v>-0.1683695587410788</v>
       </c>
       <c r="J28" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K28" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L28" t="n">
-        <v>0.006650399291310061</v>
+        <v>0.006886103843714686</v>
       </c>
       <c r="M28" t="n">
-        <v>12.89373424391609</v>
+        <v>12.77879574775106</v>
       </c>
       <c r="N28" t="n">
-        <v>255.7960192166043</v>
+        <v>253.3193022379532</v>
       </c>
       <c r="O28" t="n">
-        <v>15.99362433023248</v>
+        <v>15.91600773554578</v>
       </c>
       <c r="P28" t="n">
-        <v>290.4330148109914</v>
+        <v>290.4464728773895</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -16175,28 +16305,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.09224447873072948</v>
+        <v>-0.08915070835416952</v>
       </c>
       <c r="J29" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K29" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002223968363098128</v>
+        <v>0.002114136421245472</v>
       </c>
       <c r="M29" t="n">
-        <v>13.02419911759661</v>
+        <v>12.91941366141566</v>
       </c>
       <c r="N29" t="n">
-        <v>249.1908017744229</v>
+        <v>246.8973628538144</v>
       </c>
       <c r="O29" t="n">
-        <v>15.78577846589844</v>
+        <v>15.71296798360559</v>
       </c>
       <c r="P29" t="n">
-        <v>286.7617348361308</v>
+        <v>286.7338950429417</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -16253,28 +16383,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1373920898554293</v>
+        <v>0.1378082015198632</v>
       </c>
       <c r="J30" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K30" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L30" t="n">
-        <v>0.005808457088726127</v>
+        <v>0.005946697577896898</v>
       </c>
       <c r="M30" t="n">
-        <v>11.5102165008362</v>
+        <v>11.40484508540732</v>
       </c>
       <c r="N30" t="n">
-        <v>210.9014285816735</v>
+        <v>208.9310284381588</v>
       </c>
       <c r="O30" t="n">
-        <v>14.52244568182899</v>
+        <v>14.45444666661989</v>
       </c>
       <c r="P30" t="n">
-        <v>282.7549916586129</v>
+        <v>282.7512472104893</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -16331,28 +16461,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1069060930248857</v>
+        <v>0.1081922730465385</v>
       </c>
       <c r="J31" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K31" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00319009093780942</v>
+        <v>0.003324838282764864</v>
       </c>
       <c r="M31" t="n">
-        <v>11.77296974478529</v>
+        <v>11.67030489512175</v>
       </c>
       <c r="N31" t="n">
-        <v>233.1100420113268</v>
+        <v>230.9375699223961</v>
       </c>
       <c r="O31" t="n">
-        <v>15.2679416429107</v>
+        <v>15.19663021601816</v>
       </c>
       <c r="P31" t="n">
-        <v>281.5999344682002</v>
+        <v>281.5883605692198</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16409,28 +16539,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.03279346815052001</v>
+        <v>-0.03900492189723941</v>
       </c>
       <c r="J32" t="n">
+        <v>107</v>
+      </c>
+      <c r="K32" t="n">
         <v>106</v>
       </c>
-      <c r="K32" t="n">
-        <v>105</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0002551690408447715</v>
+        <v>0.0003671978351871275</v>
       </c>
       <c r="M32" t="n">
-        <v>12.97601792605002</v>
+        <v>12.88774483585778</v>
       </c>
       <c r="N32" t="n">
-        <v>269.9261055812601</v>
+        <v>267.519252462566</v>
       </c>
       <c r="O32" t="n">
-        <v>16.42942803573089</v>
+        <v>16.35601578816082</v>
       </c>
       <c r="P32" t="n">
-        <v>286.1297392136833</v>
+        <v>286.18669979632</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -16487,28 +16617,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3808327250692826</v>
+        <v>-0.3862556555470873</v>
       </c>
       <c r="J33" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K33" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03622391561353089</v>
+        <v>0.03785281308111665</v>
       </c>
       <c r="M33" t="n">
-        <v>12.3270388192873</v>
+        <v>12.23696408349783</v>
       </c>
       <c r="N33" t="n">
-        <v>241.1661303525754</v>
+        <v>238.9723235336167</v>
       </c>
       <c r="O33" t="n">
-        <v>15.52952447284125</v>
+        <v>15.45872968693148</v>
       </c>
       <c r="P33" t="n">
-        <v>303.295327402046</v>
+        <v>303.3462011975121</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -16565,28 +16695,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1227234480073351</v>
+        <v>-0.126558658097965</v>
       </c>
       <c r="J34" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K34" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L34" t="n">
-        <v>0.004095916010735445</v>
+        <v>0.004431559122383577</v>
       </c>
       <c r="M34" t="n">
-        <v>12.47174169909026</v>
+        <v>12.37180580006275</v>
       </c>
       <c r="N34" t="n">
-        <v>235.7308693302447</v>
+        <v>233.5390259440931</v>
       </c>
       <c r="O34" t="n">
-        <v>15.35352953982389</v>
+        <v>15.2819837044833</v>
       </c>
       <c r="P34" t="n">
-        <v>310.7069385716545</v>
+        <v>310.74199688037</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -16643,28 +16773,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.09474031217076065</v>
+        <v>-0.08913107872480854</v>
       </c>
       <c r="J35" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K35" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002171766293556421</v>
+        <v>0.001956121906051211</v>
       </c>
       <c r="M35" t="n">
-        <v>13.68921023385251</v>
+        <v>13.59498164482891</v>
       </c>
       <c r="N35" t="n">
-        <v>264.6939647669307</v>
+        <v>262.2380803830633</v>
       </c>
       <c r="O35" t="n">
-        <v>16.26941808322998</v>
+        <v>16.19376671386442</v>
       </c>
       <c r="P35" t="n">
-        <v>318.3996947605872</v>
+        <v>318.3479478451476</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -16721,28 +16851,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1376286861689236</v>
+        <v>-0.1313298408711565</v>
       </c>
       <c r="J36" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L36" t="n">
-        <v>0.005559870591247407</v>
+        <v>0.005152867677129858</v>
       </c>
       <c r="M36" t="n">
-        <v>13.11454858992312</v>
+        <v>13.02907859388295</v>
       </c>
       <c r="N36" t="n">
-        <v>220.2453493990796</v>
+        <v>218.2084656634085</v>
       </c>
       <c r="O36" t="n">
-        <v>14.84066539610268</v>
+        <v>14.77188091149561</v>
       </c>
       <c r="P36" t="n">
-        <v>335.0466555701669</v>
+        <v>334.9891100877999</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -16799,28 +16929,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.02095847003565362</v>
+        <v>-0.02108566599356557</v>
       </c>
       <c r="J37" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K37" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0001405584279946526</v>
+        <v>0.0001482034964807033</v>
       </c>
       <c r="M37" t="n">
-        <v>12.17057088916294</v>
+        <v>12.04901342025791</v>
       </c>
       <c r="N37" t="n">
-        <v>203.1309376978252</v>
+        <v>196.5573210225522</v>
       </c>
       <c r="O37" t="n">
-        <v>14.2524011204367</v>
+        <v>14.0198901929563</v>
       </c>
       <c r="P37" t="n">
-        <v>329.3389989988609</v>
+        <v>329.3399275841475</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -16858,7 +16988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL107"/>
+  <dimension ref="A1:AL108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36304,12 +36434,204 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>-34.50785325950554,173.00510659597708</t>
+          <t>-34.50789062233077,173.00498844519808</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-34.48236461818888,173.00279540302645</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>-34.48302952761015,173.0023995418302</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>-34.48372836180873,173.0020830298592</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-34.484372903132844,173.00163955990683</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-34.48515290338523,173.0014697614778</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-34.485909740902194,173.0013313779296</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-34.48666189669594,173.00130272426966</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-34.48740264336078,173.00129654307457</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-34.488144571776296,173.00140457482942</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>-34.48886844720128,173.00153833203942</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-34.4895929336666,173.00167409966312</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>-34.49033851961608,173.00169780563007</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>-34.491097715461066,173.0016098764543</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>-34.491836677657545,173.00168777845968</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>-34.49257969469195,173.0017323829283</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>-34.49331085023797,173.00187418267018</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>-34.494047913794276,173.00196749154668</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>-34.494792293455646,173.0020207325626</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>-34.49553309670139,173.00211988545158</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>-34.496263346375095,173.00227919861135</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>-34.4969998872156,173.00238267520288</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>-34.49773859280348,173.0024707969205</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>-34.49847722670776,173.00256808367453</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>-34.49922337155259,173.00267446498728</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>-34.499968232704376,173.0027916066693</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>-34.50070256086743,173.00291926801185</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>-34.50144037233483,173.00302666536163</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>-34.502163117491705,173.0032215132032</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>-34.502887399079135,173.00340740269027</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>-34.50360778790204,173.0035740820867</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>-34.504290166059825,173.00368878729327</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>-34.50497940978653,173.00383863282653</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>-34.5057088166286,173.00406308760813</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>-34.50643868572568,173.00427917624927</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>-34.50720645075815,173.00451999841636</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>-34.50791707552796,173.00490479316156</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0007/nzd0007.xlsx
+++ b/data/nzd0007/nzd0007.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL108"/>
+  <dimension ref="A1:AL109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12917,6 +12917,126 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>305.87</v>
+      </c>
+      <c r="C109" t="n">
+        <v>307.61</v>
+      </c>
+      <c r="D109" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="E109" t="n">
+        <v>314.37</v>
+      </c>
+      <c r="F109" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="G109" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="H109" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="I109" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="J109" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="K109" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="L109" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="M109" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="N109" t="n">
+        <v>348.51</v>
+      </c>
+      <c r="O109" t="n">
+        <v>346.23</v>
+      </c>
+      <c r="P109" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>334.21</v>
+      </c>
+      <c r="R109" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="S109" t="n">
+        <v>324.07</v>
+      </c>
+      <c r="T109" t="n">
+        <v>321.79</v>
+      </c>
+      <c r="U109" t="n">
+        <v>322.97</v>
+      </c>
+      <c r="V109" t="n">
+        <v>317.76</v>
+      </c>
+      <c r="W109" t="n">
+        <v>311.26</v>
+      </c>
+      <c r="X109" t="n">
+        <v>305.45</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>301.15</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>297.57</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>287.12</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>282.66</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>282.63</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>283.72</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>282.66</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>279.92</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>287.05</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>303.02</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>316.74</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12928,7 +13048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14031,6 +14151,16 @@
       </c>
       <c r="B110" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -14199,28 +14329,28 @@
         <v>0.0633</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05394948096333388</v>
+        <v>-0.05753325497686882</v>
       </c>
       <c r="J2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008215078282548527</v>
+        <v>0.0009505500623933072</v>
       </c>
       <c r="M2" t="n">
-        <v>13.18395773872977</v>
+        <v>13.05443307241998</v>
       </c>
       <c r="N2" t="n">
-        <v>244.222697478376</v>
+        <v>241.4976331240475</v>
       </c>
       <c r="O2" t="n">
-        <v>15.62762609862343</v>
+        <v>15.54019411474797</v>
       </c>
       <c r="P2" t="n">
-        <v>309.4059286092581</v>
+        <v>309.4384701192625</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14277,28 +14407,28 @@
         <v>0.047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06350151588516394</v>
+        <v>0.07178052555041457</v>
       </c>
       <c r="J3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009589331703073745</v>
+        <v>0.001244457696125245</v>
       </c>
       <c r="M3" t="n">
-        <v>13.30585983057914</v>
+        <v>13.21265068450839</v>
       </c>
       <c r="N3" t="n">
-        <v>283.3632034698821</v>
+        <v>280.453740750368</v>
       </c>
       <c r="O3" t="n">
-        <v>16.83339548248903</v>
+        <v>16.74675314054542</v>
       </c>
       <c r="P3" t="n">
-        <v>300.9404105329363</v>
+        <v>300.8631248489837</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14355,28 +14485,28 @@
         <v>0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1741124059708366</v>
+        <v>0.2008038766665892</v>
       </c>
       <c r="J4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006101049389206192</v>
+        <v>0.008162216532607625</v>
       </c>
       <c r="M4" t="n">
-        <v>14.44268306521101</v>
+        <v>14.48655678295321</v>
       </c>
       <c r="N4" t="n">
-        <v>324.8378940630272</v>
+        <v>323.9606386849056</v>
       </c>
       <c r="O4" t="n">
-        <v>18.02325980678932</v>
+        <v>17.99890659692709</v>
       </c>
       <c r="P4" t="n">
-        <v>297.045592870417</v>
+        <v>296.7898212654445</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14433,28 +14563,28 @@
         <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2440582948858199</v>
+        <v>-0.2295851603614054</v>
       </c>
       <c r="J5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0139278897468349</v>
+        <v>0.0125219934433447</v>
       </c>
       <c r="M5" t="n">
-        <v>13.8574572137703</v>
+        <v>13.79131945745488</v>
       </c>
       <c r="N5" t="n">
-        <v>298.1369238867372</v>
+        <v>295.6770261416037</v>
       </c>
       <c r="O5" t="n">
-        <v>17.26664194007443</v>
+        <v>17.19526173518751</v>
       </c>
       <c r="P5" t="n">
-        <v>311.8557090151783</v>
+        <v>311.7274912080873</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14511,28 +14641,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01832222938731723</v>
+        <v>0.03461898505183951</v>
       </c>
       <c r="J6" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" t="n">
-        <v>6.327394414484822e-05</v>
+        <v>0.000229140573737463</v>
       </c>
       <c r="M6" t="n">
-        <v>14.32359668410281</v>
+        <v>14.27541642439005</v>
       </c>
       <c r="N6" t="n">
-        <v>341.0746401787357</v>
+        <v>338.3487278375815</v>
       </c>
       <c r="O6" t="n">
-        <v>18.46820619818654</v>
+        <v>18.39425801269466</v>
       </c>
       <c r="P6" t="n">
-        <v>330.2641477467698</v>
+        <v>330.1074702223683</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14589,28 +14719,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.125820278196255</v>
+        <v>-0.1094986275777764</v>
       </c>
       <c r="J7" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002335913774387577</v>
+        <v>0.001796333997358124</v>
       </c>
       <c r="M7" t="n">
-        <v>16.16745448607763</v>
+        <v>16.06875827389444</v>
       </c>
       <c r="N7" t="n">
-        <v>400.3059735120056</v>
+        <v>396.6809640294741</v>
       </c>
       <c r="O7" t="n">
-        <v>20.00764787555013</v>
+        <v>19.91685125790405</v>
       </c>
       <c r="P7" t="n">
-        <v>349.5388169731774</v>
+        <v>349.36922613044</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14667,28 +14797,28 @@
         <v>0.1955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1067465673919814</v>
+        <v>0.1185746913485056</v>
       </c>
       <c r="J8" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K8" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002020782408766131</v>
+        <v>0.002533014824769197</v>
       </c>
       <c r="M8" t="n">
-        <v>14.41226067396791</v>
+        <v>14.29396126193524</v>
       </c>
       <c r="N8" t="n">
-        <v>331.9457246730945</v>
+        <v>328.5511982066153</v>
       </c>
       <c r="O8" t="n">
-        <v>18.21937772463962</v>
+        <v>18.12598130327336</v>
       </c>
       <c r="P8" t="n">
-        <v>346.7235736519334</v>
+        <v>346.6006298988938</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14745,28 +14875,28 @@
         <v>0.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009590946880988519</v>
+        <v>0.01777748369891509</v>
       </c>
       <c r="J9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L9" t="n">
-        <v>1.451237135208228e-05</v>
+        <v>5.073631006136115e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>14.8582248458631</v>
+        <v>14.72259940572525</v>
       </c>
       <c r="N9" t="n">
-        <v>393.8027061605298</v>
+        <v>389.6082226978223</v>
       </c>
       <c r="O9" t="n">
-        <v>19.84446285895715</v>
+        <v>19.73849595835058</v>
       </c>
       <c r="P9" t="n">
-        <v>353.5157005914318</v>
+        <v>353.434797377255</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14823,28 +14953,28 @@
         <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3650409461329495</v>
+        <v>0.3510968665570976</v>
       </c>
       <c r="J10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02150102488298866</v>
+        <v>0.02025252777226683</v>
       </c>
       <c r="M10" t="n">
-        <v>16.11119327660629</v>
+        <v>16.04773112894044</v>
       </c>
       <c r="N10" t="n">
-        <v>405.3691792806471</v>
+        <v>401.4621318818987</v>
       </c>
       <c r="O10" t="n">
-        <v>20.1337820411528</v>
+        <v>20.03651995437079</v>
       </c>
       <c r="P10" t="n">
-        <v>355.9732270477673</v>
+        <v>356.1021400377606</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14901,28 +15031,28 @@
         <v>0.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5563910940982814</v>
+        <v>0.5386851307014257</v>
       </c>
       <c r="J11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K11" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04077395114659599</v>
+        <v>0.03886009373299748</v>
       </c>
       <c r="M11" t="n">
-        <v>17.12087834870599</v>
+        <v>17.03705391024805</v>
       </c>
       <c r="N11" t="n">
-        <v>487.6712429996705</v>
+        <v>483.8661784082541</v>
       </c>
       <c r="O11" t="n">
-        <v>22.08327971565072</v>
+        <v>21.99695838992869</v>
       </c>
       <c r="P11" t="n">
-        <v>357.3288906818055</v>
+        <v>357.4916465796691</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14979,28 +15109,28 @@
         <v>0.0535</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4098755222376244</v>
+        <v>0.4302003898348787</v>
       </c>
       <c r="J12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02765887111849363</v>
+        <v>0.03077092180304497</v>
       </c>
       <c r="M12" t="n">
-        <v>15.89897933754574</v>
+        <v>15.89881407331668</v>
       </c>
       <c r="N12" t="n">
-        <v>395.4729770108664</v>
+        <v>393.0067891802565</v>
       </c>
       <c r="O12" t="n">
-        <v>19.88650238254245</v>
+        <v>19.82439883528014</v>
       </c>
       <c r="P12" t="n">
-        <v>357.4257104040685</v>
+        <v>357.2388811420507</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15057,28 +15187,28 @@
         <v>0.0434</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2635218624177769</v>
+        <v>0.248564989950928</v>
       </c>
       <c r="J13" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01272410343602948</v>
+        <v>0.01150920832144464</v>
       </c>
       <c r="M13" t="n">
-        <v>14.80406924189759</v>
+        <v>14.72834644902668</v>
       </c>
       <c r="N13" t="n">
-        <v>368.5540476654145</v>
+        <v>365.7342185609179</v>
       </c>
       <c r="O13" t="n">
-        <v>19.19776152746498</v>
+        <v>19.12417889899898</v>
       </c>
       <c r="P13" t="n">
-        <v>355.6090736410777</v>
+        <v>355.741796190594</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15135,28 +15265,28 @@
         <v>0.0688</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1879387651754064</v>
+        <v>0.1752966953254092</v>
       </c>
       <c r="J14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008559529025328416</v>
+        <v>0.007570797359553572</v>
       </c>
       <c r="M14" t="n">
-        <v>12.5085199289039</v>
+        <v>12.44145431106094</v>
       </c>
       <c r="N14" t="n">
-        <v>277.9141848018668</v>
+        <v>275.7736318006947</v>
       </c>
       <c r="O14" t="n">
-        <v>16.67075837512699</v>
+        <v>16.60643344612848</v>
       </c>
       <c r="P14" t="n">
-        <v>351.5714234208596</v>
+        <v>351.6838823236106</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15213,28 +15343,28 @@
         <v>0.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1430743008724709</v>
+        <v>0.1312054966523646</v>
       </c>
       <c r="J15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006813183144480428</v>
+        <v>0.00582311089749854</v>
       </c>
       <c r="M15" t="n">
-        <v>10.8708823680572</v>
+        <v>10.8115027679549</v>
       </c>
       <c r="N15" t="n">
-        <v>201.1389756354937</v>
+        <v>199.6986704268191</v>
       </c>
       <c r="O15" t="n">
-        <v>14.18234732459665</v>
+        <v>14.13147799866734</v>
       </c>
       <c r="P15" t="n">
-        <v>349.9562348560098</v>
+        <v>350.0621520396004</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15291,28 +15421,28 @@
         <v>0.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1628761859563641</v>
+        <v>0.1415140889959297</v>
       </c>
       <c r="J16" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K16" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L16" t="n">
-        <v>0.009572439329947446</v>
+        <v>0.007301232235405131</v>
       </c>
       <c r="M16" t="n">
-        <v>10.44581172620155</v>
+        <v>10.45785764920349</v>
       </c>
       <c r="N16" t="n">
-        <v>184.2247503486551</v>
+        <v>184.1791206023937</v>
       </c>
       <c r="O16" t="n">
-        <v>13.57294184577003</v>
+        <v>13.57126083318693</v>
       </c>
       <c r="P16" t="n">
-        <v>344.8255170179992</v>
+        <v>345.0172955471247</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -15369,28 +15499,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08805890833364226</v>
+        <v>0.07055343803924144</v>
       </c>
       <c r="J17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K17" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
-        <v>0.002578434999412682</v>
+        <v>0.001676560390106885</v>
       </c>
       <c r="M17" t="n">
-        <v>10.97105215964925</v>
+        <v>10.95987866677034</v>
       </c>
       <c r="N17" t="n">
-        <v>193.6584790904788</v>
+        <v>192.9468795920166</v>
       </c>
       <c r="O17" t="n">
-        <v>13.91612299063496</v>
+        <v>13.89053201256225</v>
       </c>
       <c r="P17" t="n">
-        <v>342.9351744168424</v>
+        <v>343.0963890618275</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -15447,28 +15577,28 @@
         <v>0.0665</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.006265175031269333</v>
+        <v>-0.01546266466345611</v>
       </c>
       <c r="J18" t="n">
+        <v>108</v>
+      </c>
+      <c r="K18" t="n">
         <v>107</v>
       </c>
-      <c r="K18" t="n">
-        <v>106</v>
-      </c>
       <c r="L18" t="n">
-        <v>1.18013998956501e-05</v>
+        <v>7.302403123754519e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>11.8085124079758</v>
+        <v>11.75708466728047</v>
       </c>
       <c r="N18" t="n">
-        <v>220.7913108713012</v>
+        <v>219.0527144662231</v>
       </c>
       <c r="O18" t="n">
-        <v>14.85904811457656</v>
+        <v>14.80042953654464</v>
       </c>
       <c r="P18" t="n">
-        <v>337.234583989311</v>
+        <v>337.3175134344102</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -15525,28 +15655,28 @@
         <v>0.0692</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09145227504300686</v>
+        <v>0.07462739027957657</v>
       </c>
       <c r="J19" t="n">
+        <v>108</v>
+      </c>
+      <c r="K19" t="n">
         <v>107</v>
       </c>
-      <c r="K19" t="n">
-        <v>106</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.002423923088222257</v>
+        <v>0.001636016127165241</v>
       </c>
       <c r="M19" t="n">
-        <v>11.6288928917828</v>
+        <v>11.61998773592051</v>
       </c>
       <c r="N19" t="n">
-        <v>221.334445565265</v>
+        <v>220.3083551769988</v>
       </c>
       <c r="O19" t="n">
-        <v>14.87731311646243</v>
+        <v>14.84278798531458</v>
       </c>
       <c r="P19" t="n">
-        <v>332.384417400023</v>
+        <v>332.5402151085011</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -15603,28 +15733,28 @@
         <v>0.0704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1290036082514321</v>
+        <v>0.1179064126387384</v>
       </c>
       <c r="J20" t="n">
+        <v>108</v>
+      </c>
+      <c r="K20" t="n">
         <v>107</v>
       </c>
-      <c r="K20" t="n">
-        <v>106</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.00421147935358035</v>
+        <v>0.00357582445451643</v>
       </c>
       <c r="M20" t="n">
-        <v>13.18682677287711</v>
+        <v>13.13058551797084</v>
       </c>
       <c r="N20" t="n">
-        <v>253.0282105828275</v>
+        <v>251.1169637270173</v>
       </c>
       <c r="O20" t="n">
-        <v>15.90686048794128</v>
+        <v>15.84667043031492</v>
       </c>
       <c r="P20" t="n">
-        <v>325.4840403803628</v>
+        <v>325.5867999339229</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -15681,28 +15811,28 @@
         <v>0.0697</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2987962187178296</v>
+        <v>0.2960297447764611</v>
       </c>
       <c r="J21" t="n">
+        <v>108</v>
+      </c>
+      <c r="K21" t="n">
         <v>107</v>
       </c>
-      <c r="K21" t="n">
-        <v>106</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02223906976025969</v>
+        <v>0.02221153947158017</v>
       </c>
       <c r="M21" t="n">
-        <v>13.14600846891402</v>
+        <v>13.039140973506</v>
       </c>
       <c r="N21" t="n">
-        <v>252.4056346994337</v>
+        <v>250.0748877938615</v>
       </c>
       <c r="O21" t="n">
-        <v>15.88727902126206</v>
+        <v>15.81375628349765</v>
       </c>
       <c r="P21" t="n">
-        <v>316.9270280149411</v>
+        <v>316.9526454445217</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -15759,28 +15889,28 @@
         <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3041885984799714</v>
+        <v>0.302112216577237</v>
       </c>
       <c r="J22" t="n">
+        <v>108</v>
+      </c>
+      <c r="K22" t="n">
         <v>107</v>
       </c>
-      <c r="K22" t="n">
-        <v>106</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.02583402222243392</v>
+        <v>0.0259267822588507</v>
       </c>
       <c r="M22" t="n">
-        <v>12.32946385594571</v>
+        <v>12.2269952219669</v>
       </c>
       <c r="N22" t="n">
-        <v>224.3673105302775</v>
+        <v>222.2862967590817</v>
       </c>
       <c r="O22" t="n">
-        <v>14.97889550435136</v>
+        <v>14.90926882040436</v>
       </c>
       <c r="P22" t="n">
-        <v>311.1412033512477</v>
+        <v>311.160430558264</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -15837,28 +15967,28 @@
         <v>0.0565</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1337568651847172</v>
+        <v>0.1336075220052362</v>
       </c>
       <c r="J23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K23" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005404073692697242</v>
+        <v>0.005487282853343212</v>
       </c>
       <c r="M23" t="n">
-        <v>11.59915492676645</v>
+        <v>11.49054688659595</v>
       </c>
       <c r="N23" t="n">
-        <v>215.3698314511603</v>
+        <v>213.338123424887</v>
       </c>
       <c r="O23" t="n">
-        <v>14.67548402783228</v>
+        <v>14.60609884345875</v>
       </c>
       <c r="P23" t="n">
-        <v>307.8628388301797</v>
+        <v>307.8642005468122</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -15915,28 +16045,28 @@
         <v>0.061</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1842121396057775</v>
+        <v>0.1821971214095766</v>
       </c>
       <c r="J24" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K24" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L24" t="n">
-        <v>0.007644773826501083</v>
+        <v>0.007612786589306197</v>
       </c>
       <c r="M24" t="n">
-        <v>13.52364251890126</v>
+        <v>13.40450968921322</v>
       </c>
       <c r="N24" t="n">
-        <v>275.3814166575919</v>
+        <v>272.7477483038741</v>
       </c>
       <c r="O24" t="n">
-        <v>16.59462011187939</v>
+        <v>16.5150763941277</v>
       </c>
       <c r="P24" t="n">
-        <v>301.8759116837339</v>
+        <v>301.8950812189003</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -15993,28 +16123,28 @@
         <v>0.0519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1376479996141705</v>
+        <v>0.1383209991858137</v>
       </c>
       <c r="J25" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K25" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004412559566954521</v>
+        <v>0.004535320152229683</v>
       </c>
       <c r="M25" t="n">
-        <v>13.38198426936529</v>
+        <v>13.25851507017232</v>
       </c>
       <c r="N25" t="n">
-        <v>270.515493823352</v>
+        <v>267.9407634903055</v>
       </c>
       <c r="O25" t="n">
-        <v>16.44735522275092</v>
+        <v>16.36889622089118</v>
       </c>
       <c r="P25" t="n">
-        <v>297.1417381101057</v>
+        <v>297.1354191017825</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -16071,28 +16201,28 @@
         <v>0.0309</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5403368487190764</v>
+        <v>0.5416614307632335</v>
       </c>
       <c r="J26" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K26" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L26" t="n">
-        <v>0.03916743079005869</v>
+        <v>0.0400352574528231</v>
       </c>
       <c r="M26" t="n">
-        <v>17.61345374736327</v>
+        <v>17.45033366440788</v>
       </c>
       <c r="N26" t="n">
-        <v>451.5885767241456</v>
+        <v>447.2103845261531</v>
       </c>
       <c r="O26" t="n">
-        <v>21.25061356112208</v>
+        <v>21.14734934988669</v>
       </c>
       <c r="P26" t="n">
-        <v>282.6549679725146</v>
+        <v>282.6424491443535</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -16149,28 +16279,28 @@
         <v>0.0427</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2913985649210444</v>
+        <v>0.2849943940234518</v>
       </c>
       <c r="J27" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K27" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01395822995634755</v>
+        <v>0.01358955489479041</v>
       </c>
       <c r="M27" t="n">
-        <v>15.50184817510471</v>
+        <v>15.39797651419291</v>
       </c>
       <c r="N27" t="n">
-        <v>386.3465356352244</v>
+        <v>382.7447607472017</v>
       </c>
       <c r="O27" t="n">
-        <v>19.65569982562881</v>
+        <v>19.5638636456913</v>
       </c>
       <c r="P27" t="n">
-        <v>283.4899490935372</v>
+        <v>283.5495550851913</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -16227,28 +16357,28 @@
         <v>0.0517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1683695587410788</v>
+        <v>-0.1739407841952238</v>
       </c>
       <c r="J28" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K28" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" t="n">
-        <v>0.006886103843714686</v>
+        <v>0.007474562206252089</v>
       </c>
       <c r="M28" t="n">
-        <v>12.77879574775106</v>
+        <v>12.69550791363122</v>
       </c>
       <c r="N28" t="n">
-        <v>253.3193022379532</v>
+        <v>250.9908232670744</v>
       </c>
       <c r="O28" t="n">
-        <v>15.91600773554578</v>
+        <v>15.84268989998461</v>
       </c>
       <c r="P28" t="n">
-        <v>290.4464728773895</v>
+        <v>290.4998158362446</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -16305,28 +16435,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.08915070835416952</v>
+        <v>-0.09189459604494715</v>
       </c>
       <c r="J29" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K29" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002114136421245472</v>
+        <v>0.002284882486894957</v>
       </c>
       <c r="M29" t="n">
-        <v>12.91941366141566</v>
+        <v>12.81717733661109</v>
       </c>
       <c r="N29" t="n">
-        <v>246.8973628538144</v>
+        <v>244.6398530113821</v>
       </c>
       <c r="O29" t="n">
-        <v>15.71296798360559</v>
+        <v>15.64096713798038</v>
       </c>
       <c r="P29" t="n">
-        <v>286.7338950429417</v>
+        <v>286.7587471200209</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -16383,28 +16513,28 @@
         <v>0.0708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1378082015198632</v>
+        <v>0.1337560830535847</v>
       </c>
       <c r="J30" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K30" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L30" t="n">
-        <v>0.005946697577896898</v>
+        <v>0.005699746097559411</v>
       </c>
       <c r="M30" t="n">
-        <v>11.40484508540732</v>
+        <v>11.32566747767286</v>
       </c>
       <c r="N30" t="n">
-        <v>208.9310284381588</v>
+        <v>207.058804536917</v>
       </c>
       <c r="O30" t="n">
-        <v>14.45444666661989</v>
+        <v>14.38953802374895</v>
       </c>
       <c r="P30" t="n">
-        <v>282.7512472104893</v>
+        <v>282.787948260899</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -16461,28 +16591,28 @@
         <v>0.0684</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1081922730465385</v>
+        <v>0.1054842576710843</v>
       </c>
       <c r="J31" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K31" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L31" t="n">
-        <v>0.003324838282764864</v>
+        <v>0.003215685961279524</v>
       </c>
       <c r="M31" t="n">
-        <v>11.67030489512175</v>
+        <v>11.57875878477596</v>
       </c>
       <c r="N31" t="n">
-        <v>230.9375699223961</v>
+        <v>228.8270936237308</v>
       </c>
       <c r="O31" t="n">
-        <v>15.19663021601816</v>
+        <v>15.1270318841381</v>
       </c>
       <c r="P31" t="n">
-        <v>281.5883605692198</v>
+        <v>281.6128877417672</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -16539,28 +16669,28 @@
         <v>0.0701</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.03900492189723941</v>
+        <v>-0.04722220224303401</v>
       </c>
       <c r="J32" t="n">
+        <v>108</v>
+      </c>
+      <c r="K32" t="n">
         <v>107</v>
       </c>
-      <c r="K32" t="n">
-        <v>106</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0003671978351871275</v>
+        <v>0.0005470456747832531</v>
       </c>
       <c r="M32" t="n">
-        <v>12.88774483585778</v>
+        <v>12.81163699106971</v>
       </c>
       <c r="N32" t="n">
-        <v>267.519252462566</v>
+        <v>265.2695076690217</v>
       </c>
       <c r="O32" t="n">
-        <v>16.35601578816082</v>
+        <v>16.28709635475341</v>
       </c>
       <c r="P32" t="n">
-        <v>286.18669979632</v>
+        <v>286.2625381886655</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -16617,28 +16747,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3862556555470873</v>
+        <v>-0.3961896192242702</v>
       </c>
       <c r="J33" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K33" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03785281308111665</v>
+        <v>0.04036335591632745</v>
       </c>
       <c r="M33" t="n">
-        <v>12.23696408349783</v>
+        <v>12.17055229687462</v>
       </c>
       <c r="N33" t="n">
-        <v>238.9723235336167</v>
+        <v>237.0721856131497</v>
       </c>
       <c r="O33" t="n">
-        <v>15.45872968693148</v>
+        <v>15.39714861957076</v>
       </c>
       <c r="P33" t="n">
-        <v>303.3462011975121</v>
+        <v>303.439980035896</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -16695,28 +16825,28 @@
         <v>0.0675</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.126558658097965</v>
+        <v>-0.1335133470037266</v>
       </c>
       <c r="J34" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K34" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L34" t="n">
-        <v>0.004431559122383577</v>
+        <v>0.00501217871583659</v>
       </c>
       <c r="M34" t="n">
-        <v>12.37180580006275</v>
+        <v>12.28861104400119</v>
       </c>
       <c r="N34" t="n">
-        <v>233.5390259440931</v>
+        <v>231.5152123372834</v>
       </c>
       <c r="O34" t="n">
-        <v>15.2819837044833</v>
+        <v>15.21562395491172</v>
       </c>
       <c r="P34" t="n">
-        <v>310.74199688037</v>
+        <v>310.8059822833261</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -16773,28 +16903,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.08913107872480854</v>
+        <v>-0.08798932012349152</v>
       </c>
       <c r="J35" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K35" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L35" t="n">
-        <v>0.001956121906051211</v>
+        <v>0.001939804854265592</v>
       </c>
       <c r="M35" t="n">
-        <v>13.59498164482891</v>
+        <v>13.47197907822746</v>
       </c>
       <c r="N35" t="n">
-        <v>262.2380803830633</v>
+        <v>259.7213997262209</v>
       </c>
       <c r="O35" t="n">
-        <v>16.19376671386442</v>
+        <v>16.11587415333778</v>
       </c>
       <c r="P35" t="n">
-        <v>318.3479478451476</v>
+        <v>318.3373456177258</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -16851,28 +16981,28 @@
         <v>0.0713</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1313298408711565</v>
+        <v>-0.1298436525854989</v>
       </c>
       <c r="J36" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K36" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L36" t="n">
-        <v>0.005152867677129858</v>
+        <v>0.005126353280069496</v>
       </c>
       <c r="M36" t="n">
-        <v>13.02907859388295</v>
+        <v>12.91161086589002</v>
       </c>
       <c r="N36" t="n">
-        <v>218.2084656634085</v>
+        <v>216.0773753472042</v>
       </c>
       <c r="O36" t="n">
-        <v>14.77188091149561</v>
+        <v>14.69957058376891</v>
       </c>
       <c r="P36" t="n">
-        <v>334.9891100877999</v>
+        <v>334.9754417481196</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -16929,28 +17059,28 @@
         <v>0.0823</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.02108566599356557</v>
+        <v>-0.01129930314052824</v>
       </c>
       <c r="J37" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K37" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0001482034964807033</v>
+        <v>4.324034005875887e-05</v>
       </c>
       <c r="M37" t="n">
-        <v>12.04901342025791</v>
+        <v>11.99210812374794</v>
       </c>
       <c r="N37" t="n">
-        <v>196.5573210225522</v>
+        <v>194.9862079075925</v>
       </c>
       <c r="O37" t="n">
-        <v>14.0198901929563</v>
+        <v>13.96374619891068</v>
       </c>
       <c r="P37" t="n">
-        <v>329.3399275841475</v>
+        <v>329.2499232872484</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -16988,7 +17118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL108"/>
+  <dimension ref="A1:AL109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36635,6 +36765,198 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-34.48236461818888,173.00279540302645</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>-34.48302952761015,173.0023995418302</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>-34.48372836180873,173.0020830298592</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-34.484372903132844,173.00163955990683</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-34.48515290338523,173.0014697614778</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-34.485909740902194,173.0013313779296</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-34.48666189669594,173.00130272426966</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-34.48740264336078,173.00129654307457</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-34.48814483139888,173.00125492842733</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>-34.48888484942607,173.00132720346213</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>-34.4895929336666,173.00167409966312</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>-34.49036188806631,173.00150622051208</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>-34.49110033093115,173.00158843338232</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>-34.49183579706952,173.0016949980495</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>-34.49258236273908,173.00171050845378</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>-34.49331651494056,173.00182773941987</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>-34.49405305278687,173.00192535820725</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>-34.49479735311746,173.0019812281225</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>-34.49553562850406,173.00210151239006</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>-34.49626521379531,173.00226599221423</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>-34.497002878132086,173.00236152330922</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>-34.4977424946657,173.0024432025837</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>-34.49848232273712,173.00253255825794</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>-34.499228145640274,173.00264440441825</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>-34.499968232704376,173.0027916066693</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>-34.5007121845731,173.00286338514303</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>-34.50144512910251,173.00299904362802</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>-34.50216993127956,173.0031819466043</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>-34.50289267015355,173.0033767943101</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>-34.503612232503066,173.0035469388886</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>-34.50429182704015,173.0036730099618</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>-34.504981243518614,173.00380591826814</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>-34.50571009601531,173.00404026330207</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>-34.50644031241986,173.00425015652507</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>-34.5072119394421,173.00448977882215</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>-34.50793448569091,173.00484973747365</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
